--- a/SINGLE HADITH CONTENT/missing_input/[V1] TIRMIDHI-(MADANI)-BANGLA_missing.xlsx
+++ b/SINGLE HADITH CONTENT/missing_input/[V1] TIRMIDHI-(MADANI)-BANGLA_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C229"/>
+  <dimension ref="A1:C285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4309,6 +4309,958 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَحْمَدُ بْنُ مُحَمَّدِ بْنِ مُوسَى الْمُلَقَّبُ، مَرْدَوَيْهِ قَالَ أَخْبَرَنَا ابْنُ الْمُبَارَكِ، أَخْبَرَنَا عَبْدُ الرَّحْمَنِ بْنُ زِيَادِ بْنِ أَنْعُمَ، أَنَّ عَبْدَ الرَّحْمَنِ بْنَ رَافِعٍ، وَبَكْرَ بْنَ سَوَادَةَ، أَخْبَرَاهُ عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ إِذَا أَحْدَثَ - يَعْنِي الرَّجُلَ - وَقَدْ جَلَسَ فِي آخِرِ صَلاَتِهِ قَبْلَ أَنْ يُسَلِّمَ فَقَدْ جَازَتْ صَلاَتُهُ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ إِسْنَادُهُ لَيْسَ بِذَاكَ الْقَوِيِّ وَقَدِ اضْطَرَبُوا فِي إِسْنَادِهِ ‏.‏ وَقَدْ ذَهَبَ بَعْضُ أَهْلِ الْعِلْمِ إِلَى هَذَا ‏.‏ قَالُوا إِذَا جَلَسَ مِقْدَارَ التَّشَهُّدِ وَأَحْدَثَ قَبْلَ أَنْ يُسَلِّمَ فَقَدْ تَمَّتْ صَلاَتُهُ ‏.‏ وَقَالَ بَعْضُ أَهْلِ الْعِلْمِ إِذَا أَحْدَثَ قَبْلَ أَنْ يَتَشَهَّدَ وَقَبْلَ أَنْ يُسَلِّمَ أَعَادَ الصَّلاَةَ ‏.‏ وَهُوَ قَوْلُ الشَّافِعِيِّ ‏.‏ وَقَالَ أَحْمَدُ إِذَا لَمْ يَتَشَهَّدْ وَسَلَّمَ أَجْزَأَهُ لِقَوْلِ النَّبِيِّ صلى الله عليه وسلم ‏"‏ وَتَحْلِيلُهَا التَّسْلِيمُ ‏"‏ وَالتَّشَهُّدُ أَهْوَنُ قَامَ النَّبِيُّ صلى الله عليه وسلم فِي اثْنَتَيْنِ فَمَضَى فِي صَلاَتِهِ وَلَمْ يَتَشَهَّدْ ‏.‏ وَقَالَ إِسْحَاقُ بْنُ إِبْرَاهِيمَ إِذَا تَشَهَّدَ وَلَمْ يُسَلِّمْ أَجْزَأَهُ ‏.‏ وَاحْتَجَّ بِحَدِيثِ ابْنِ مَسْعُودٍ حِينَ عَلَّمَهُ النَّبِيُّ صلى الله عليه وسلم التَّشَهُّدَ فَقَالَ ‏"‏ إِذَا فَرَغْتَ مِنْ هَذَا فَقَدْ قَضَيْتَ مَا عَلَيْكَ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَعَبْدُ الرَّحْمَنِ بْنُ زِيَادِ بْنِ أَنْعُمٍ هُوَ الإِفْرِيقِيُّ وَقَدْ ضَعَّفَهُ بَعْضُ أَهْلِ الْحَدِيثِ مِنْهُمْ يَحْيَى بْنُ سَعِيدٍ الْقَطَّانُ وَأَحْمَدُ بْنُ حَنْبَلٍ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ কোন ব্যক্তি যদি নামাজের শেষে (তাশাহুদ এর জন্য) বসে সালাম ফিরানোর পূর্বে বাতকর্ম করে তবে তার নামাজ জায়িয হবে (নতুন করে আদায় করতে হবে না)।</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2221</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا وَاصِلُ بْنُ عَبْدِ الأَعْلَى، حَدَّثَنَا مُحَمَّدُ بْنُ الْفُضَيْلِ، عَنِ الأَعْمَشِ، عَنْ عَلِيِّ بْنِ مُدْرِكٍ، عَنْ هِلاَلِ بْنِ يِسَافٍ، عَنْ عِمْرَانَ بْنِ حُصَيْنٍ، قَالَ سَمِعْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم يَقُولُ ‏ "‏ خَيْرُ النَّاسِ قَرْنِي ثُمَّ الَّذِينَ يَلُونَهُمْ ثُمَّ الَّذِينَ يَلُونَهُمْ ثُمَّ يَأْتِي مِنْ بَعْدِهِمْ قَوْمٌ يَتَسَمَّنُونَ وَيُحِبُّونَ السِّمَنَ يُعْطُونَ الشَّهَادَةَ قَبْلَ أَنْ يُسْأَلُوهَا ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَكَذَا رَوَى مُحَمَّدُ بْنُ فُضَيْلٍ هَذَا الْحَدِيثَ عَنِ الأَعْمَشِ عَنْ عَلِيِّ بْنِ مُدْرِكٍ عَنْ هِلاَلِ بْنِ يِسَافٍ وَرَوَى غَيْرُ وَاحِدٍ مِنَ الْحُفَّاظِ هَذَا الْحَدِيثَ عَنِ الأَعْمَشِ عَنْ هِلاَلِ بْنِ يِسَافٍ وَلَمْ يَذْكُرُوا فِيهِ عَلِيَّ بْنَ مُدْرِكٍ ‏.‏ قَالَ وَحَدَّثَنَا الْحُسَيْنُ بْنُ حُرَيْثٍ، حَدَّثَنَا وَكِيعٌ، عَنِ الأَعْمَشِ، حَدَّثَنَا هِلاَلُ بْنُ يِسَافٍ، عَنْ عِمْرَانَ بْنِ حُصَيْنٍ، عَنِ النَّبِيِّ صلى الله عليه وسلم فَذَكَرَ نَحْوَهُ ‏.‏ وَهَذَا أَصَحُّ عِنْدِي مِنْ حَدِيثِ مُحَمَّدِ بْنِ فُضَيْلٍ وَقَدْ رُوِيَ مِنْ غَيْرِ وَجْهٍ عَنْ عِمْرَانَ بْنِ حُصَيْنٍ عَنِ النَّبِيِّ صلى الله عليه وسلم ‏.‏</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>আমি রাসূলুল্লাহ (صلى الله عليه وسلم)-কে বলতে শুনেছি: আমার জামানাই হলো সর্বোৎকৃষ্ট জামানা, তারপর এর নিকটবর্তীদের জামানা, তারপর এর নিকটবর্তীদের জামানা। তারপর এমন যুগের আগমন ঘটবে যখনকার লোকেরা হবে মোটা দেহবিশিষ্ট এবং তারা মোটা দেহের অধিকারী হতে পছন্দ করবে। সাক্ষ্য চাওয়া না হলেও তারা সাক্ষ্য প্রদান করবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا قُتَيْبَةُ بْنُ سَعِيدٍ، حَدَّثَنَا أَبُو عَوَانَةَ، عَنْ قَتَادَةَ، عَنْ زُرَارَةَ بْنِ أَوْفَى، عَنْ عِمْرَانَ بْنِ حُصَيْنٍ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ خَيْرُ أُمَّتِي الْقَرْنُ الَّذِي بُعِثْتُ فِيهِمْ ثُمَّ الَّذِينَ يَلُونَهُمْ ‏"‏ ‏.‏ قَالَ وَلاَ أَعْلَمُ ذَكَرَ الثَّالِثَ أَمْ لاَ ‏"‏ ثُمَّ يَنْشَأُ أَقْوَامٌ يَشْهَدُونَ وَلاَ يُسْتَشْهَدُونَ وَيَخُونُونَ وَلاَ يُؤْتَمَنُونَ وَيَفْشُو فِيهِمُ السِّمَنُ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ আমি যে যুগে যাদের মাঝে প্রেরিত হয়েছি সেই যুগের আমার উম্মতই হলো শ্রেষ্ঠ; তারপর তাদের পরবর্তী যুগের লোক। বর্ণনাকারী বলেন, তৃতীয় যুগের কথা বলা হয়েছে কিনা তা আমি জানি না। তারপর এমন কিছু মানুষের আগমন ঘটবে যাদের নিকট সাক্ষ্য চাওয়া না হলেও তারা সাক্ষ্য প্রদান করবে। তারা খিয়ানত করবে, আমানত রক্ষা করবে না এবং তাদের মধ্যে মোটা দেহবিশিষ্ট মানুষের বিস্তার ঘটবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَبُو كُرَيْبٍ، مُحَمَّدُ بْنُ الْعَلاَءِ حَدَّثَنَا عُمَرُ بْنُ عُبَيْدٍ الطَّنَافِسِيُّ، عَنْ سِمَاكِ بْنِ حَرْبٍ، عَنْ جَابِرِ بْنِ سَمُرَةَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ يَكُونُ مِنْ بَعْدِي اثْنَا عَشَرَ أَمِيرًا ‏"‏ ‏.‏ قَالَ ثُمَّ تَكَلَّمَ بِشَيْءٍ لَمْ أَفْهَمْهُ فَسَأَلْتُ الَّذِي يَلِينِي فَقَالَ قَالَ ‏"‏ كُلُّهُمْ مِنْ قُرَيْشٍ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏ حَدَّثَنَا أَبُو كُرَيْبٍ، حَدَّثَنَا عُمَرُ بْنُ عُبَيْدٍ، عَنْ أَبِيهِ، عَنْ أَبِي بَكْرِ بْنِ أَبِي مُوسَى، عَنْ جَابِرِ بْنِ سَمُرَةَ، عَنِ النَّبِيِّ صلى الله عليه وسلم مِثْلَ هَذَا الْحَدِيثِ وقَدْ رُوِيَ مِنْ غَيْرِ وَجْهٍ عَنْ جَابِرِ بْنِ سَمُرَةَ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ يُسْتَغْرَبُ مِنْ حَدِيثِ أَبِي بَكْرِ بْنِ أَبِي مُوسَى عَنْ جَابِرِ بْنِ سَمُرَةَ ‏.‏ وَفِي الْبَابِ عَنِ ابْنِ مَسْعُودٍ وَعَبْدِ اللَّهِ بْنِ عَمْرٍو ‏.‏</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ আমার পরে বারোজন শাসক হবে। বর্ণনাকারী বলেন, তারপর তিনি কি বললেন, আমি তা বুঝতে পারিনি। তাই আমি আমার কাছের একজন লোককে প্রশ্ন করলাম। তিনি বললেন যে, রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ তাদের সকলেই কুরাইশ বংশীয় হবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2224</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا بُنْدَارٌ، حَدَّثَنَا أَبُو دَاوُدَ، حَدَّثَنَا حُمَيْدُ بْنُ مِهْرَانَ، عَنْ سَعْدِ بْنِ أَوْسٍ، عَنْ زِيَادِ بْنِ كُسَيْبٍ الْعَدَوِيِّ، قَالَ كُنْتُ مَعَ أَبِي بَكْرَةَ تَحْتَ مِنْبَرِ ابْنِ عَامِرٍ وَهُوَ يَخْطُبُ وَعَلَيْهِ ثِيَابٌ رِقَاقٌ فَقَالَ أَبُو بِلاَلٍ انْظُرُوا إِلَى أَمِيرِنَا يَلْبَسُ ثِيَابَ الْفُسَّاقِ ‏.‏ فَقَالَ أَبُو بَكْرَةَ اسْكُتْ سَمِعْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم يَقُولُ ‏ "‏ مَنْ أَهَانَ سُلْطَانَ اللَّهِ فِي الأَرْضِ أَهَانَهُ اللَّهُ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>আমি ইবন আমিরের মিম্বরের নিকট আবু বকরা (রাঃ)-এর সাথে বসা ছিলাম। সে সময় তিনি সূক্ষ্ম মিহি পোশাক পরিহিত অবস্থায় ভাষণ দিচ্ছিলেন। আবু বিলাল বললেন, তোমরা আমাদের শাসকের প্রতি লক্ষ্য করে দেখ, তিনি গুনাহগারদের অনুরূপ পোশাক পরেছেন। আবু বকরা (রাঃ) বললেন, “তুমি চুপ থাক, আমি রাসূলুল্লাহ (صلى الله عليه وسلم) কে বলতে শুনেছি: দুনিয়াতে আল্লাহর নিযুক্ত শাসককে যে ব্যক্তি অপমান করবে, আল্লাহ তাকে অপমান করবেন।”</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا يَحْيَى بْنُ مُوسَى، حَدَّثَنَا عَبْدُ الرَّزَّاقِ، أَخْبَرَنَا مَعْمَرٌ، عَنِ الزُّهْرِيِّ، عَنْ سَالِمِ بْنِ عَبْدِ اللَّهِ بْنِ عُمَرَ، عَنْ أَبِيهِ، قَالَ قِيلَ لِعُمَرَ بْنِ الْخَطَّابِ لَوِ اسْتَخْلَفْتَ قَالَ إِنْ أَسْتَخْلِفْ فَقَدِ اسْتَخْلَفَ أَبُو بَكْرٍ وَإِنْ لَمْ أَسْتَخْلِفْ لَمْ يَسْتَخْلِفْ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏.‏ قَالَ أَبُو عِيسَى وَفِي الْحَدِيثِ قِصَّةٌ طَوِيلَةٌ ‏.‏ وَهَذَا حَدِيثٌ صَحِيحٌ قَدْ رُوِيَ مِنْ غَيْرِ وَجْهٍ عَنِ ابْنِ عُمَرَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>উমর ইবনু খাত্তাব (রাঃ)-কে বলা হলো, আপনি যদি আপনার পরবর্তী খলিফা (প্রতিনিধি) মনোনীত করে যেতেন। তিনি বললেন, আমি যদি পরবর্তী খলিফা মনোনীত করি তাহলে আবু বকর (রাঃ)-ও পরবর্তী খলিফা মনোনীত করেছিলেন। আর আমি যদি পরবর্তী খলিফা মনোনীত না করে যাই (তাও যথার্থ হবে), কেননা রাসূলুল্লাহ (صلى الله عليه وسلم) কাউকে খলিফা মনোনীত করে যাননি।</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2226</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَحْمَدُ بْنُ مَنِيعٍ، حَدَّثَنَا سُرَيْجُ بْنُ النُّعْمَانِ، حَدَّثَنَا حَشْرَجُ بْنُ نُبَاتَةَ، عَنْ سَعِيدِ بْنِ جُمْهَانَ، قَالَ حَدَّثَنِي سَفِينَةُ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ الْخِلاَفَةُ فِي أُمَّتِي ثَلاَثُونَ سَنَةً ثُمَّ مُلْكٌ بَعْدَ ذَلِكَ ‏"‏ ‏.‏ ثُمَّ قَالَ لِي سَفِينَةُ أَمْسِكْ خِلاَفَةَ أَبِي بَكْرٍ وَخِلاَفَةَ عُمَرَ وَخِلاَفَةَ عُثْمَانَ ‏.‏ ثُمَّ قَالَ لِي أَمْسِكْ خِلاَفَةَ عَلِيٍّ ‏.‏ قَالَ فَوَجَدْنَاهَا ثَلاَثِينَ سَنَةً ‏.‏ قَالَ سَعِيدٌ فَقُلْتُ لَهُ إِنَّ بَنِي أُمَيَّةَ يَزْعُمُونَ أَنَّ الْخِلاَفَةَ فِيهِمْ ‏.‏ قَالَ كَذَبُوا بَنُو الزَّرْقَاءِ بَلْ هُمْ مُلُوكٌ مِنْ شَرِّ الْمُلُوكِ ‏.‏ قَالَ أَبُو عِيسَى وَفِي الْبَابِ عَنْ عُمَرَ وَعَلِيٍّ قَالاَ لَمْ يَعْهَدِ النَّبِيُّ صلى الله عليه وسلم فِي الْخِلاَفَةِ شَيْئًا ‏.‏ وَهَذَا حَدِيثٌ حَسَنٌ قَدْ رَوَاهُ غَيْرُ وَاحِدٍ عَنْ سَعِيدِ بْنِ جُمْهَانَ وَلاَ نَعْرِفُهُ إِلاَّ مِنْ حَدِيثِ سَعِيدِ بْنِ جُمْهَانَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>সাফিনা (রাঃ) আমার নিকট বর্ণনা করেন যে, রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ আমার উম্মতের খিলাফাতের সময়কাল (শাসনকাল) হবে ত্রিশ বছর, তারপর হবে রাজতন্ত্র।</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2227</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا حُسَيْنُ بْنُ مُحَمَّدٍ الْبَصْرِيُّ، حَدَّثَنَا خَالِدُ بْنُ الْحَارِثِ، حَدَّثَنَا شُعْبَةُ، عَنْ حَبِيبِ بْنِ الزُّبَيْرِ، قَالَ سَمِعْتُ عَبْدَ اللَّهِ بْنَ أَبِي الْهُذَيْلِ، يَقُولُ كَانَ نَاسٌ مِنْ رَبِيعَةَ عِنْدَ عَمْرِو بْنِ الْعَاصِي فَقَالَ رَجُلٌ مِنْ بَكْرِ بْنِ وَائِلٍ لَتَنْتَهِيَنَّ قُرَيْشٌ أَوْ لَيَجْعَلَنَّ اللَّهُ هَذَا الأَمْرَ فِي جُمْهُورٍ مِنَ الْعَرَبِ غَيْرِهِمْ ‏.‏ فَقَالَ عَمْرُو بْنُ الْعَاصِي كَذَبْتَ سَمِعْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم يَقُولُ ‏ "‏ قُرَيْشٌ وُلاَةُ النَّاسِ فِي الْخَيْرِ وَالشَّرِّ إِلَى يَوْمِ الْقِيَامَةِ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَفِي الْبَابِ عَنِ ابْنِ مَسْعُودٍ وَابْنِ عُمَرَ وَجَابِرٍ ‏.‏ وَهَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>আমি আবদুল্লাহ ইবনু আবু হুযাইল (রহঃ)-কে বলতে শুনেছি: আমর ইবনুল আস (রাঃ)-এর সামনে রাবিয়া বংশের কয়েকজন লোক উপস্থিত ছিল। বাকর ইবনু ওয়াইল বংশের কোন একজন লোক বলল, অবশ্যই অন্যায় কাজ হতে কুরাইশদের বিরত থাকা উচিত। তা না হলে আল্লাহ তাআলা এ (খিলাফাতের) দায়িত্ব আরবদের মাঝে অন্যদেরকে প্রদান করবেন। আমর ইবনুল আস (রাঃ) বলেন, তুমি ভুল বলেছ। রাসূলুল্লাহ (صلى الله عليه وسلم)-কে আমি বলতে শুনেছি: কেয়ামতের দিন পর্যন্ত কুরাইশগণ ভাল-মন্দ সর্বাবস্থায় জনগণের নেতৃত্ব দিবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ بَشَّارٍ الْعَبْدِيُّ، حَدَّثَنَا أَبُو بَكْرٍ الْحَنَفِيُّ، عَنْ عَبْدِ الْحَمِيدِ بْنِ جَعْفَرٍ، عَنْ عُمَرَ بْنِ الْحَكَمِ، قَالَ سَمِعْتُ أَبَا هُرَيْرَةَ، يَقُولُ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ لاَ يَذْهَبُ اللَّيْلُ وَالنَّهَارُ حَتَّى يَمْلِكَ رَجُلٌ مِنَ الْمَوَالِي يُقَالُ لَهُ جَهْجَاهُ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ ‘জাহজাহ’ নামক কোন এক মুক্তদাস অধিপতি না হওয়া পর্যন্ত দিন-রাতের অবসান (কেয়ামত) হবে না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2229</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا قُتَيْبَةُ بْنُ سَعِيدٍ، حَدَّثَنَا حَمَّادُ بْنُ زَيْدٍ، عَنْ أَيُّوبَ، عَنْ أَبِي قِلاَبَةَ، عَنْ أَبِي أَسْمَاءَ الرَّحَبِيِّ، عَنْ ثَوْبَانَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ إِنَّمَا أَخَافُ عَلَى أُمَّتِي الأَئِمَّةَ الْمُضِلِّينَ ‏"‏ ‏.‏ قَالَ وَقَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ لاَ تَزَالُ طَائِفَةٌ مِنْ أُمَّتِي عَلَى الْحَقِّ ظَاهِرِينَ لاَ يَضُرُّهُمْ مَنْ يَخْذُلُهُمْ حَتَّى يَأْتِيَ أَمْرُ اللَّهِ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَهَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏ قَالَ سَمِعْتُ مُحَمَّدَ بْنَ إِسْمَاعِيلَ يَقُولُ سَمِعْتُ عَلِيَّ بْنَ الْمَدِينِيِّ يَقُولُ وَذَكَرَ هَذَا الْحَدِيثَ عَنِ النَّبِيِّ صلى الله عليه وسلم ‏"‏ لاَ تَزَالُ طَائِفَةٌ مِنْ أُمَّتِي ظَاهِرِينَ عَلَى الْحَقِّ ‏"‏ ‏.‏ فَقَالَ عَلِيٌّ هُمْ أَهْلُ الْحَدِيثِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন: আমি আমার উম্মতের ব্যাপারে পথভ্রষ্টকারী নেতাদেরকেই ভয় করি। রাসূলুল্লাহ (صلى الله عليه وسلم) আরও বলেছেন: আমার উম্মতের এক দল লোক আল্লাহর হুকুম (কেয়ামত) আসার পূর্ব মুহূর্ত পর্যন্ত সর্বদা বিজয়ীবেশে সত্যের উপর প্রতিষ্ঠিত থাকবে। যারা তাদের অপমানিত করতে চাইবে তারা তাদের ক্ষতি করতে পারবে না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عُبَيْدُ بْنُ أَسْبَاطِ بْنِ مُحَمَّدٍ الْقُرَشِيُّ الْكُوفِيُّ، قَالَ حَدَّثَنِي أَبِي، حَدَّثَنَا سُفْيَانُ الثَّوْرِيُّ، عَنْ عَاصِمِ بْنِ بَهْدَلَةَ، عَنْ زِرٍّ، عَنْ عَبْدِ اللَّهِ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ لاَ تَذْهَبُ الدُّنْيَا حَتَّى يَمْلِكَ الْعَرَبَ رَجُلٌ مِنْ أَهْلِ بَيْتِي يُوَاطِئُ اسْمُهُ اسْمِي ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَفِي الْبَابِ عَنْ عَلِيٍّ وَأَبِي سَعِيدٍ وَأُمِّ سَلَمَةَ وَأَبِي هُرَيْرَةَ ‏.‏ وَهَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ আমার পরিবারের একজন আরবের অধিপতি না হওয়া পর্যন্ত পৃথিবী ধ্বংস হবে না। আমার নামের অনুরূপই তার নাম হবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2231</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَبْدُ الْجَبَّارِ بْنُ الْعَلاَءِ بْنِ عَبْدِ الْجَبَّارِ الْعَطَّارُ، حَدَّثَنَا سُفْيَانُ بْنُ عُيَيْنَةَ، عَنْ عَاصِمٍ، عَنْ زِرٍّ، عَنْ عَبْدِ اللَّهِ، عَنِ النَّبِيِّ صلى الله عليه وسلم قَالَ ‏ "‏ يَلِي رَجُلٌ مِنْ أَهْلِ بَيْتِي يُوَاطِئُ اسْمُهُ اسْمِي ‏"‏ ‏.‏ قَالَ عَاصِمٌ وَأَخْبَرَنَا أَبُو صَالِحٍ، عَنْ أَبِي هُرَيْرَةَ، قَالَ لَوْ لَمْ يَبْقَ مِنَ الدُّنْيَا إِلاَّ يَوْمٌ لَطَوَّلَ اللَّهُ ذَلِكَ الْيَوْمَ حَتَّى يَلِيَ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم) বলেছেনঃ আমার পরিবারের মধ্যে একজন লোক রাজাধিপতি হবে, তার নাম হবে আমার নামের অনুরূপ। আসিম (রহঃ) বলেনঃ আবু হুরাইরা (রাঃ) হতে আবু সালিহ (রহঃ) আমাদের নিকট বর্ণনা করেছেন যে, যদি পৃথিবী ধ্বংসের মাত্র একদিনও অবশিষ্ট থাকে, তাহলে তার রাজত্বের জন্য আল্লাহ তা’আলা সে দিনটিকেই দীর্ঘায়িত করে দিবেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2232</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ بَشَّارٍ، حَدَّثَنَا مُحَمَّدُ بْنُ جَعْفَرٍ، حَدَّثَنَا شُعْبَةُ، قَالَ سَمِعْتُ زَيْدًا الْعَمِّيَّ، قَالَ سَمِعْتُ أَبَا الصِّدِّيقِ النَّاجِيَّ، يُحَدِّثُ عَنْ أَبِي سَعِيدٍ الْخُدْرِيِّ، قَالَ خَشِينَا أَنْ يَكُونَ، بَعْدَ نَبِيِّنَا حَدَثٌ فَسَأَلْنَا نَبِيَّ اللَّهِ صلى الله عليه وسلم فَقَالَ ‏"‏ إِنَّ فِي أُمَّتِي الْمَهْدِيَّ يَخْرُجُ يَعِيشُ خَمْسًا أَوْ سَبْعًا أَوْ تِسْعًا ‏"‏ ‏.‏ زَيْدٌ الشَّاكُّ ‏.‏ قَالَ قُلْنَا وَمَا ذَاكَ قَالَ ‏"‏ سِنِينَ ‏"‏ ‏.‏ قَالَ ‏"‏ فَيَجِيءُ إِلَيْهِ رَجُلٌ فَيَقُولُ يَا مَهْدِيُّ أَعْطِنِي أَعْطِنِي ‏"‏ ‏.‏ قَالَ ‏"‏ فَيَحْثِي لَهُ فِي ثَوْبِهِ مَا اسْتَطَاعَ أَنْ يَحْمِلَهُ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ وَقَدْ رُوِيَ مِنْ غَيْرِ وَجْهٍ عَنْ أَبِي سَعِيدٍ عَنِ النَّبِيِّ صلى الله عليه وسلم ‏.‏ وَأَبُو الصِّدِّيقِ النَّاجِيُّ اسْمُهُ بَكْرُ بْنُ عَمْرٍو وَيُقَالُ بَكْرُ بْنُ قَيْسٍ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>আমরা ভয় পাচ্ছিলাম যে, আমাদের রাসূল (صلى الله عليه وسلم)-এর পরে নতুন কোন দুর্ঘটনা ঘটবে। সুতরাং আমরা এ বিষয়ে রাসূলুল্লাহ (صلى الله عليه وسلم) কে প্রশ্ন করলাম। তিনি বললেনঃ আমার উম্মাতের মাঝে মাহদীর আগমন ঘটবে, সে পাঁচ অথবা সাত অথবা নয় বছর পর্যন্ত বেঁচে থাকবে (যাইদ সন্দেহে পতিত হয়েছে যে, উর্ধ্বতন বর্ণনাকারী কোন সংখ্যাটি বলেছেন)। বর্ণনাকারী বলেন, আমরা প্রশ্ন করলাম, এই সংখ্যায় কি বুঝায়? তিনি বললেনঃ বছর। মানুষ তার নিকট এসে বলবে, হে মাহদি! আমাকে কিছু দান করুন, আমাকে কিছু দান করুন। রাসূলুল্লাহ (صلى الله عليه وسلم) বলেন, তারপর সে তার কাপড় বা থলেতে যেটুকু পরিমাণ বহন করে নিতে পারবে তিনি তাকে সেটুকু পরিমাণ দান করবেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2233</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا قُتَيْبَةُ، حَدَّثَنَا اللَّيْثُ بْنُ سَعْدٍ، عَنِ ابْنِ شِهَابٍ، عَنْ سَعِيدِ بْنِ الْمُسَيَّبِ، عَنْ أَبِي هُرَيْرَةَ، أَنَّ رَسُولَ اللَّهِ صلى الله عليه وسلم قَالَ ‏ "‏ وَالَّذِي نَفْسِي بِيَدِهِ لَيُوشِكَنَّ أَنْ يَنْزِلَ فِيكُمُ ابْنُ مَرْيَمَ حَكَمًا مُقْسِطًا فَيَكْسِرَ الصَّلِيبَ وَيَقْتُلَ الْخِنْزِيرَ وَيَضَعَ الْجِزْيَةَ وَيَفِيضَ الْمَالُ حَتَّى لاَ يَقْبَلَهُ أَحَدٌ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ সেই মহান সত্তার শপথ যাঁর হাতে আমার প্রাণ! তোমাদের মাঝে ঈসা ইবনে মারইয়াম (আঃ) খুব শীঘ্রই ন্যায়বিচারক শাসক হিসাবে অবতরণ করবেন। তিনি ক্রুশ ভঙ্গ করবেন, শুকর হত্যা করবেন এবং জিযিয়া বাতিল করবেন। তখন এতই ধন-সম্পদের প্রাচুর্য হবে যে, কেউ তা গ্রহণ করবে না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2234</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَبْدُ اللَّهِ بْنُ مُعَاوِيَةَ الْجُمَحِيُّ، حَدَّثَنَا حَمَّادُ بْنُ سَلَمَةَ، عَنْ خَالِدٍ الْحَذَّاءِ، عَنْ عَبْدِ اللَّهِ بْنِ شَقِيقٍ، عَنْ عَبْدِ اللَّهِ بْنِ سُرَاقَةَ، عَنْ أَبِي عُبَيْدَةَ بْنِ الْجَرَّاحِ، قَالَ سَمِعْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم يَقُولُ ‏"‏ إِنَّهُ لَمْ يَكُنْ نَبِيٌّ بَعْدَ نُوحٍ إِلاَّ قَدْ أَنْذَرَ الدَّجَّالَ قَوْمَهُ وَإِنِّي أُنْذِرُكُمُوهُ ‏"‏ ‏.‏ فَوَصَفَهُ لَنَا رَسُولُ اللَّهِ صلى الله عليه وسلم فَقَالَ ‏"‏ لَعَلَّهُ سَيُدْرِكُهُ بَعْضُ مَنْ رَآنِي أَوْ سَمِعَ كَلاَمِي ‏"‏ ‏.‏ قَالُوا يَا رَسُولَ اللَّهِ فَكَيْفَ قُلُوبُنَا يَوْمَئِذٍ قَالَ ‏"‏ مِثْلُهَا يَعْنِي الْيَوْمَ أَوْ خَيْرٌ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَفِي الْبَابِ عَنْ عَبْدِ اللَّهِ بْنِ بُسْرٍ وَعَبْدِ اللَّهِ بْنِ الْحَارِثِ بْنِ جُزَىٍّ وَعَبْدِ اللَّهِ بْنِ مُغَفَّلٍ وَأَبِي هُرَيْرَةَ ‏.‏ وَهَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ مِنْ حَدِيثِ أَبِي عُبَيْدَةَ بْنِ الْجَرَّاحِ لاَ نَعْرِفُهُ إِلاَّ مِنْ حَدِيثِ خَالِدٍ الْحَذَّاءِ وَقَدْ رَوَاهُ شُعْبَةُ أَيْضًا عَنْ خَالِدٍ الْحَذَّاءِ ‏.‏ وَأَبُو عُبَيْدَةَ بْنُ الْجَرَّاحِ اسْمُهُ عَامِرُ بْنُ عَبْدِ اللَّهِ بْنِ الْجَرَّاحِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>আমি রাসূলুল্লাহ (صلى الله عليه وسلم)-কে বলতে শুনেছি: নূহ (আঃ)-এর পর হতে এমন কোন নবী আসেননি যিনি দাজ্জাল প্রসঙ্গে তাঁর জাতিকে সতর্ক করেননি। আর আমিও তোমাদেরকে তার (দাজ্জাল) প্রসঙ্গে সতর্ক করে দিচ্ছি। তারপর রাসূলুল্লাহ (صلى الله عليه وسلم) আমাদের নিকটে দাজ্জালের পরিচয় বর্ণনা করলেন তারপর তিনি বললেন, যারা আমাকে দেখেছ বা আমার কথা শুনেছ তাদের কেউ হয়তো তার সাক্ষাত পাবে। উপস্থিত জনতা প্রশ্ন করল, হে আল্লাহর রাসূল! সে সময় আমাদের অন্তরের অবস্থা কেমন হবে? তিনি বললেনঃ বর্তমানে যে রকম আছে সেই রকম বা তার চেয়েও ভাল হবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَبْدُ بْنُ حُمَيْدٍ، أَخْبَرَنَا عَبْدُ الرَّزَّاقِ، أَخْبَرَنَا مَعْمَرٌ، عَنِ الزُّهْرِيِّ، عَنْ سَالِمٍ، عَنِ ابْنِ عُمَرَ، قَالَ قَامَ رَسُولُ اللَّهِ صلى الله عليه وسلم فِي النَّاسِ فَأَثْنَى عَلَى اللَّهِ بِمَا هُوَ أَهْلُهُ ثُمَّ ذَكَرَ الدَّجَّالَ فَقَالَ ‏"‏ إِنِّي لأُنْذِرُكُمُوهُ وَمَا مِنْ نَبِيٍّ إِلاَّ وَقَدْ أَنْذَرَ قَوْمَهُ وَلَقَدْ أَنْذَرَهُ نُوحٌ قَوْمَهُ وَلَكِنِّي سَأَقُولُ لَكُمْ فِيهِ قَوْلاً لَمْ يَقُلْهُ نَبِيٌّ لِقَوْمِهِ تَعْلَمُونَ أَنَّهُ أَعْوَرُ وَإِنَّ اللَّهَ لَيْسَ بِأَعْوَرَ ‏"‏ ‏.‏ قَالَ الزُّهْرِيُّ وَأَخْبَرَنِي عُمَرُ بْنُ ثَابِتٍ الأَنْصَارِيُّ، أَنَّهُ أَخْبَرَهُ بَعْضُ، أَصْحَابِ النَّبِيِّ صلى الله عليه وسلم أَنَّ النَّبِيَّ صلى الله عليه وسلم قَالَ يَوْمَئِذٍ لِلنَّاسِ وَهُوَ يُحَذِّرُهُمْ فِتْنَتَهُ ‏"‏ تَعْلَمُونَ أَنَّهُ لَنْ يَرَى أَحَدٌ مِنْكُمْ رَبَّهُ حَتَّى يَمُوتَ وَإِنَّهُ مَكْتُوبٌ بَيْنَ عَيْنَيْهِ ك ف ر يَقْرَأُهُ مَنْ كَرِهَ عَمَلَهُ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>কোন একদিন জনগনের মাঝে খুতবা দেয়ার উদ্দেশ্যে রাসূলুল্লাহ (صلى الله عليه وسلم) দাঁড়ালেন। তিনি আল্লাহ তাআলার যথোপযুক্ত প্রশংসা করার পর দাজ্জালের প্রসঙ্গ উল্লেখ করে বললেনঃ আমি অবশ্যই দাজ্জাল সম্পর্কে তোমাদেরকে সতর্ক করছি। আর এমন কোন নবী অতিবাহিত হননি যিনি তাঁর জাতিকে দাজ্জাল সম্পর্কে সতর্ক করেননি, এমনকি নূহ (আঃ)-ও তাঁর সম্প্রদায়কে দাজ্জালের ব্যাপারে সতর্ক করেছেন। কিন্তু আমি তার ব্যাপারে এমন একটি কথা বলতে চাই যা আর কোন নবী তাঁর জাতিকে বলেননি। নিশ্চয়ই সে হবে অন্ধ। অথচ আল্লাহ তো অন্ধ নন। যুহরী (রহঃ) বলেন, আমাকে উমর ইবনু সাবিত আনসারি (রহঃ) বলেছেন, রাসূলুল্লাহ (صلى الله عليه وسلم) এর কয়েকজন সাহাবী তার নিকট বর্ণনা করেছেন যে, সেদিন জনগণকে ফিতনা প্রসঙ্গে সাবধান করতে গিয়ে রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন, জেনে রাখ, তোমাদের কেউই মৃত্যুর আগে তার প্রভুকে দেখতে পাবে না, বিশেষত তার (দাজ্জালের) দুই চোখের মধ্যবর্তী স্থানে ‘কাফির’ শব্দটি লিখিত থাকবে। যে তার কাণ্ডকীর্তি অপছন্দ করবে, সে তা পড়তে সক্ষম হবে। আবূ ঈসা বলেন, এ হাদীসটি হাসান সহীহ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَبْدُ بْنُ حُمَيْدٍ، حَدَّثَنَا عَبْدُ الرَّزَّاقِ، أَخْبَرَنَا مَعْمَرٌ، عَنِ الزُّهْرِيِّ، عَنْ سَالِمٍ، عَنِ ابْنِ عُمَرَ، أَنَّ رَسُولَ اللَّهِ صلى الله عليه وسلم قَالَ ‏ "‏ تُقَاتِلُكُمُ الْيَهُودُ فَتُسَلَّطُونَ عَلَيْهِمْ حَتَّى يَقُولَ الْحَجَرُ يَا مُسْلِمُ هَذَا يَهُودِيٌّ وَرَائِي فَاقْتُلْهُ ‏"‏ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>রসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ ইয়াহুদিরা তোমাদের সাথে যুদ্ধ করবে। তাতে তোমরা তাদের বিরুদ্ধে জয় লাভ করবে। এমনকি পাথর পর্যন্ত বলবে, হে মুসলিম! এই যে আমার অন্তরালে এক ইয়াহুদি (লুকিয়ে) আছে, তাকে হত্যা কর।</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2237</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ بَشَّارٍ، وَأَحْمَدُ بْنُ مَنِيعٍ، قَالاَ حَدَّثَنَا رَوْحُ بْنُ عُبَادَةَ، حَدَّثَنَا سَعِيدُ بْنُ أَبِي عَرُوبَةَ، عَنْ أَبِي التَّيَّاحِ، عَنِ الْمُغِيرَةِ بْنِ سُبَيْعٍ، عَنْ عَمْرِو بْنِ حُرَيْثٍ، عَنْ أَبِي بَكْرٍ الصِّدِّيقِ، قَالَ حَدَّثَنَا رَسُولُ اللَّهِ صلى الله عليه وسلم قَالَ ‏ "‏ الدَّجَّالُ يَخْرُجُ مِنْ أَرْضٍ بِالْمَشْرِقِ يُقَالُ لَهَا خُرَاسَانُ يَتْبَعُهُ أَقْوَامٌ كَأَنَّ وُجُوهَهُمُ الْمَجَانُّ الْمُطْرَقَةُ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَفِي الْبَابِ عَنْ أَبِي هُرَيْرَةَ وَعَائِشَةَ ‏.‏ وَهَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ ‏.‏ وَقَدْ رَوَاهُ عَبْدُ اللَّهِ بْنُ شَوْذَبٍ وَغَيْرُ وَاحِدٍ عَنْ أَبِي التَّيَّاحِ وَلاَ نَعْرِفُهُ إِلاَّ مِنْ حَدِيثِ أَبِي التَّيَّاحِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) আমাদেরকে বলেছেনঃ প্রাচ্যের খোরাসান হতে দাজ্জালের আবির্ভাব ঘটবে। এমন কতক জাতি তার অনুসরণ করবে, যাদের মুখমণ্ডল হবে স্তরবিশিষ্ট চওড়া ঢালের মতো।</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2238</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَبْدُ اللَّهِ بْنُ عَبْدِ الرَّحْمَنِ، أَخْبَرَنَا الْحَكَمُ بْنُ الْمُبَارَكِ، حَدَّثَنَا الْوَلِيدُ بْنُ مُسْلِمٍ، عَنْ أَبِي بَكْرِ بْنِ أَبِي مَرْيَمَ، عَنِ الْوَلِيدِ بْنِ سُفْيَانَ، عَنْ يَزِيدَ بْنِ قُطَيْبٍ السَّكُونِيِّ، عَنْ أَبِي بَحْرِيَّةَ، صَاحِبِ مُعَاذٍ عَنْ مُعَاذِ بْنِ جَبَلٍ، عَنِ النَّبِيِّ صلى الله عليه وسلم قَالَ ‏ "‏ الْمَلْحَمَةُ الْعُظْمَى وَفَتْحُ الْقُسْطَنْطِينِيَّةِ وَخُرُوجُ الدَّجَّالِ فِي سَبْعَةِ أَشْهُرٍ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَفِي الْبَابِ عَنِ الصَّعْبِ بْنِ جَثَّامَةَ وَعَبْدِ اللَّهِ بْنِ بُسْرٍ وَعَبْدِ اللَّهِ بْنِ مَسْعُودٍ وَأَبِي سَعِيدٍ الْخُدْرِيِّ ‏.‏ وَهَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ لاَ نَعْرِفُهُ إِلاَّ مِنْ هَذَا الْوَجْهِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেন: মহা হত্যাকাণ্ড, কনস্টান্টিনোপল বিজয় এবং দাজ্জালের আবির্ভাব ঘটবে সাত মাসের মধ্যে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2239</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مَحْمُودُ بْنُ غَيْلاَنَ، حَدَّثَنَا أَبُو دَاوُدَ، عَنْ شُعْبَةَ، عَنْ يَحْيَى بْنِ سَعِيدٍ، عَنْ أَنَسِ بْنِ مَالِكٍ، قَالَ فَتْحُ الْقُسْطُنْطِينِيَّةِ مَعَ قِيَامِ السَّاعَةِ ‏.‏ قَالَ هَذَا حَدِيثٌ غَرِيبٌ ‏.‏ وَالْقُسْطَنْطِينِيَّةُ هِيَ مَدِينَةُ الرُّومِ تُفْتَحُ عِنْدَ خُرُوجِ الدَّجَّالِ وَالْقُسْطَنْطِينِيَّةُ قَدْ فُتِحَتْ فِي زَمَانِ بَعْضِ أَصْحَابِ النَّبِيِّ صلى الله عليه وسلم ‏.‏</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>হাদিসটি বর্ণনা করেছেন মাহমুদ ইবন গায়লান, আবু দাউদ, শু’বা, ইয়াহিয়া ইবন সঈদ, আনাস ইবন মালিক (রাঃ) থেকে। কনস্টান্টিনোপল বিজয় সংঘটিত হবে কেয়ামতের কাছাকাছি সময়ে। মাহমুদ ইবন গায়লান বলেন, হাদিসটি গরীব। কনস্টান্টিনোপল হল রোম নগরী। দাজ্জালের আবির্ভাবকালে তা বিজিত হবে। কনস্টান্টিনোপল নবী (صلى الله عليه وسلم)-এর কোন কোন সাহাবীর সময়ে বিজিত হয়েছে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2240</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَلِيُّ بْنُ حُجْرٍ، أَخْبَرَنَا الْوَلِيدُ بْنُ مُسْلِمٍ، وَعَبْدُ اللَّهِ بْنُ عَبْدِ الرَّحْمَنِ بْنِ يَزِيدَ بْنِ جَابِرٍ، دَخَلَ حَدِيثُ أَحَدِهِمَا فِي حَدِيثِ الآخَرِ عَنْ عَبْدِ الرَّحْمَنِ بْنِ يَزِيدَ بْنِ جَابِرٍ عَنْ يَحْيَى بْنِ جَابِرٍ الطَّائِيِّ عَنْ عَبْدِ الرَّحْمَنِ بْنِ جُبَيْرٍ عَنْ أَبِيهِ جُبَيْرِ بْنِ نُفَيْرٍ عَنِ النَّوَّاسِ بْنِ سَمْعَانَ الْكِلاَبِيِّ قَالَ ذَكَرَ رَسُولُ اللَّهِ صلى الله عليه وسلم الدَّجَّالَ ذَاتَ غَدَاةٍ فَخَفَّضَ فِيهِ وَرَفَّعَ حَتَّى ظَنَنَّاهُ فِي طَائِفَةِ النَّخْلِ ‏.‏ قَالَ فَانْصَرَفْنَا مِنْ عِنْدِ رَسُولِ اللَّهِ صلى الله عليه وسلم ثُمَّ رَجَعْنَا إِلَيْهِ فَعَرَفَ ذَلِكَ فِينَا فَقَالَ ‏"‏ مَا شَأْنُكُمْ ‏"‏ ‏.‏ قَالَ قُلْنَا يَا رَسُولَ اللَّهِ ذَكَرْتَ الدَّجَّالَ الْغَدَاةَ فَخَفَّضْتَ فِيهِ وَرَفَّعْتَ حَتَّى ظَنَنَّاهُ فِي طَائِفَةِ النَّخْلِ ‏.‏ قَالَ ‏"‏ غَيْرُ الدَّجَّالِ أَخْوَفُ لِي عَلَيْكُمْ إِنْ يَخْرُجْ وَأَنَا فِيكُمْ فَأَنَا حَجِيجُهُ دُونَكُمْ وَإِنْ يَخْرُجْ وَلَسْتُ فِيكُمْ فَامْرُؤٌ حَجِيجُ نَفْسِهِ وَاللَّهُ خَلِيفَتِي عَلَى كُلِّ مُسْلِمٍ إِنَّهُ شَابٌّ قَطَطٌ عَيْنُهُ قَائِمَةٌ شَبِيهٌ بِعَبْدِ الْعُزَّى بْنِ قَطَنٍ فَمَنْ رَآهُ مِنْكُمْ فَلْيَقْرَأْ فَوَاتِحَ سُورَةِ أَصْحَابِ الْكَهْفِ قَالَ يَخْرُجُ مَا بَيْنَ الشَّامِ وَالْعِرَاقِ فَعَاثَ يَمِينًا وَشِمَالاً يَا عِبَادَ اللَّهِ اثْبُتُوا ‏"‏ ‏.‏ قَالَ قُلْنَا يَا رَسُولَ اللَّهِ وَمَا لُبْثُهُ فِي الأَرْضِ قَالَ ‏"‏ أَرْبَعِينَ يَوْمًا يَوْمٌ كَسَنَةٍ وَيَوْمٌ كَشَهْرٍ وَيَوْمٌ كَجُمُعَةٍ وَسَائِرُ أَيَّامِهُ كَأَيَّامِكُمْ ‏"‏ ‏.‏ قَالَ قُلْنَا يَا رَسُولَ اللَّهِ أَرَأَيْتَ الْيَوْمَ الَّذِي كَالسَّنَةِ أَتَكْفِينَا فِيهِ صَلاَةُ يَوْمٍ قَالَ ‏"‏ لاَ وَلَكِنِ اقْدُرُوا لَهُ ‏"‏ ‏.‏ قَالَ قُلْنَا يَا رَسُولَ اللَّهِ فَمَا سُرْعَتُهُ فِي الأَرْضِ قَالَ ‏"‏ كَالْغَيْثِ اسْتَدْبَرَتْهُ الرِّيحُ فَيَأْتِي الْقَوْمَ فَيَدْعُوهُمْ فَيُكَذِّبُونَهُ وَيَرُدُّونَ عَلَيْهِ قَوْلَهُ فَيَنْصَرِفُ عَنْهُمْ فَتَتْبَعُهُ أَمْوَالُهُمْ فَيُصْبِحُونَ لَيْسَ بِأَيْدِيهِمْ شَيْءٌ ثُمَّ يَأْتِي الْقَوْمَ فَيَدْعُوهُمْ فَيَسْتَجِيبُونَ لَهُ وَيُصَدِّقُونَهُ فَيَأْمُرُ السَّمَاءَ أَنْ تُمْطِرَ فَتُمْطِرَ وَيَأْمُرُ الأَرْضَ أَنْ تُنْبِتَ فَتُنْبِتَ فَتَرُوحُ عَلَيْهِمْ سَارِحَتُهُمْ كَأَطْوَلِ مَا كَانَتْ ذُرًى وَأَمَدِّهِ خَوَاصِرَ وَأَدَرِّهِ ضُرُوعًا قَالَ ثُمَّ يَأْتِي الْخَرِبَةَ فَيَقُولُ لَهَا أَخْرِجِي كُنُوزَكِ فَيَنْصَرِفُ مِنْهَا فَتَتْبَعُهُ كَيَعَاسِيبِ النَّحْلِ ثُمَّ يَدْعُو رَجُلاً شَابًّا مُمْتَلِئًا شَبَابًا فَيَضْرِبُهُ بِالسَّيْفِ فَيَقْطَعُهُ جِزْلَتَيْنِ ثُمَّ يَدْعُوهُ فَيُقْبِلُ يَتَهَلَّلُ وَجْهُهُ يَضْحَكُ فَبَيْنَمَا هُوَ كَذَلِكَ إِذْ هَبَطَ عِيسَى ابْنُ مَرْيَمَ عَلَيْهِ السَّلاَمُ بِشَرْقِيِّ دِمَشْقَ عِنْدَ الْمَنَارَةِ الْبَيْضَاءِ بَيْنَ مَهْرُودَتَيْنِ وَاضِعًا يَدَيْهِ عَلَى أَجْنِحَةِ مَلَكَيْنِ إِذَا طَأْطَأَ رَأْسَهُ قَطَرَ وَإِذَا رَفَعَهُ تَحَدَّرَ مِنْهُ جُمَانٌ كَاللُّؤْلُؤِ قَالَ وَلاَ يَجِدُ رِيحَ نَفَسِهِ يَعْنِي أَحَدٌ إِلاَّ مَاتَ وَرِيحُ نَفَسِهِ مُنْتَهَى بَصَرِهِ قَالَ فَيَطْلُبُهُ حَتَّى يُدْرِكَهُ بِبَابِ لُدٍّ فَيَقْتُلَهُ قَالَ فَيَلْبَثُ كَذَلِكَ مَا شَاءَ اللَّهُ ‏.‏ قَالَ ثُمَّ يُوحِي اللَّهُ إِلَيْهِ أَنْ حَرِّزْ عِبَادِي إِلَى الطُّورِ فَإِنِّي قَدْ أَنْزَلْتُ عِبَادًا لِي لاَ يَدَانِ لأَحَدٍ بِقِتَالِهِمْ ‏.‏ قَالَ وَيَبْعَثُ اللَّهُ يَأْجُوجَ وَمَأْجُوجَ وَهُمْ كَمَا قَالَ اللَّهُ‏:‏ ‏(‏ مِنْ كُلِّ حَدَبٍ يَنْسِلُونَ ‏)‏ ‏.‏ قَالَ فَيَمُرُّ أَوَّلُهُمْ بِبُحَيْرَةِ الطَّبَرِيَّةِ فَيَشْرَبُ مَا فِيهَا ثُمَّ يَمُرُّ بِهَا آخِرُهُمْ فَيَقُولُ لَقَدْ كَانَ بِهَذِهِ مَرَّةً مَاءٌ ثُمَّ يَسِيرُونَ حَتَّى يَنْتَهُوا إِلَى جَبَلِ بَيْتِ الْمَقْدِسِ فَيَقُولُونَ لَقَدْ قَتَلْنَا مَنْ فِي الأَرْضِ هَلُمَّ فَلْنَقْتُلْ مَنْ فِي السَّمَاءِ ‏.‏ فَيَرْمُونَ بِنُشَّابِهِمْ إِلَى السَّمَاءِ فَيَرُدُّ اللَّهُ عَلَيْهِمْ نُشَّابَهُمْ مُحْمَرًّا دَمًا وَيُحَاصَرُ عِيسَى ابْنُ مَرْيَمَ وَأَصْحَابُهُ حَتَّى يَكُونَ رَأْسُ الثَّوْرِ يَوْمَئِذٍ خَيْرًا لأَحَدِهِمْ مِنْ مِائَةِ دِينَارٍ لأَحَدِكُمُ الْيَوْمَ ‏.‏ قَالَ فَيَرْغَبُ عِيسَى ابْنُ مَرْيَمَ إِلَى اللَّهِ وَأَصْحَابُهُ قَالَ فَيُرْسِلُ اللَّهُ إِلَيْهِمُ النَّغَفَ فِي رِقَابِهِمْ فَيُصْبِحُونَ فَرْسَى مَوْتَى كَمَوْتِ نَفْسٍ وَاحِدَةٍ قَالَ وَيَهْبِطُ عِيسَى وَأَصْحَابُهُ فَلاَ يَجِدُ مَوْضِعَ شِبْرٍ إِلاَّ وَقَدْ مَلأَتْهُ زَهَمَتُهُمْ وَنَتَنُهُمْ وَدِمَاؤُهُمْ قَالَ فَيَرْغَبُ عِيسَى إِلَى اللَّهِ وَأَصْحَابُهُ قَالَ فَيُرْسِلُ اللَّهُ عَلَيْهِمْ طَيْرًا كَأَعْنَاقِ الْبُخْتِ قَالَ فَتَحْمِلُهُمْ فَتَطْرَحُهُمْ بِالْمَهْبِلِ وَيَسْتَوْقِدُ الْمُسْلِمُونَ مِنْ قِسِيِّهِمْ وَنُشَّابِهِمْ وَجِعَابِهِمْ سَبْعَ سِنِينَ قَالَ وَيُرْسِلُ اللَّهُ عَلَيْهِمْ مَطَرًا لاَ يَكُنُّ مِنْهُ بَيْتُ وَبَرٍ وَلاَ مَدَرٍ قَالَ فَيَغْسِلُ الأَرْضَ فَيَتْرُكُهَا كَالزَّلَفَةِ قَالَ ثُمَّ يُقَالُ لِلأَرْضِ أَخْرِجِي ثَمَرَتَكِ وَرُدِّي بَرَكَتَكِ ‏.‏ فَيَوْمَئِذٍ تَأْكُلُ الْعِصَابَةُ مِنَ الرُّمَّانَةِ وَيَسْتَظِلُّونَ بِقِحْفِهَا وَيُبَارَكُ فِي الرِّسْلِ حَتَّى إِنَّ الْفِئَامَ مِنَ النَّاسِ لَيَكْتَفُونَ بِاللَّقْحَةِ مِنَ الإِبِلِ وَإِنَّ الْقَبِيلَةَ لَيَكْتَفُونَ بِاللَّقْحَةِ مِنَ الْبَقَرِ وَإِنَّ الْفَخِذَ لَيَكْتَفُونَ بِاللَّقْحَةِ مِنَ الْغَنَمِ فَبَيْنَمَا هُمْ كَذَلِكَ إِذْ بَعَثَ اللَّهُ رِيحًا فَقَبَضَتْ رُوحَ كُلِّ مُؤْمِنٍ وَيَبْقَى سَائِرُ النَّاسِ يَتَهَارَجُونَ كَمَا تَتَهَارَجُ الْحُمُرُ فَعَلَيْهِمْ تَقُومُ السَّاعَةُ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ غَرِيبٌ لاَ نَعْرِفُهُ إِلاَّ مِنْ حَدِيثِ عَبْدِ الرَّحْمَنِ بْنِ يَزِيدَ بْنِ جَابِرٍ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) কোন এক সকালে দাজ্জাল প্রসঙ্গে আলোচনা করেন। তিনি এর ভয়াবহতা ও নিকৃষ্টতা তুলে ধরেন। এমনকি আমাদের ধারণা সৃষ্টি হলো যে, সে হয়তো খেজুর বাগানের ওপাশেই বিদ্যমান। বর্ণনাকারী বলেন, আমরা রাসূলুল্লাহ (صلى الله عليه وسلم) এর নিকট হতে চলে গেলাম, তারপর আবার আমরা তাঁর নিকট ফিরে এলাম। তিনি আমাদের মধ্যে দাজ্জালের ভীতির চিহ্ন দেখে প্রশ্ন করেনঃ তোমাদের কি হয়েছে? আমরা বললাম, হে আল্লাহর রাসূল (صلى الله عليه وسلم)! আপনি সকালে দাজ্জাল প্রসঙ্গে আলোচনা করেছেন এবং এর ভয়াবহতা ও নিকৃষ্টতা এমন ভাষায় উত্থাপন করেছেন যে, আমাদের ধারণা হচ্ছিল যে, হয়তো সে খেজুর বাগানের পাশেই উপস্থিত আছে। তিনি বললেনঃ তোমাদের ক্ষেত্রে দাজ্জাল ছাড়াও আমার আরো কিছু আশংকা রয়েছে। যদি সে আমার জীবদ্দশাতেই তোমাদের মাঝে আসে তাহলে আমিই তোমাদের পক্ষে তার প্রতিপক্ষ হবো। আর সে যদি আমার অবর্তমানে আবির্ভূত হয়, তাহলে তোমরাই তার প্রতিপক্ষ হবে। আর আল্লাহই প্রত্যেক মুসলিমের জন্য আমার পরিবর্তে সহায় হবেন। সে (দাজ্জাল) হবে কুঞ্চিত (কোঁকড়া) চুলবিশিষ্ট, স্থির দৃষ্টিসম্পন্ন যুবক, সে হবে আব্দুল উযযা ইবনু কাতানের অনুরূপ। তোমাদের মধ্যে কেউ যদি তার দেখা পায় তাহলে যেন সে সূরা কাহফ-এর প্রাথমিক আয়াতগুলো তিলাওয়াত করে। তিনি বললেনঃ সে সিরিয়া ও ইরাকের মধ্যবর্তী কোন এলাকা হতে আত্মপ্রকাশ করবে। তারপর সে ডানে-বামে ফিতনা ফ্যাসাদ ও বিপর্যয় সৃষ্টি করে বেড়াবে। হে আল্লাহর বান্দাগণ! তোমরা দৃঢ়তার সাথে অবস্থান করবে। আমরা প্রশ্ন করলাম, হে আল্লাহর রাসূল (صلى الله عليه وسلم)! সে কত দিন দুনিয়াতে থাকবে? তিনি বললেনঃ চল্লিশ দিন। এর একদিন হবে এক বছরের সমান, একদিন হবে এক মাসের সমান এবং একদিন হবে এক সপ্তাহের সমান, আর অবশিষ্ট দিনগুলো হবে তোমাদের বর্তমান দিনের মতো। বর্ণনাকারী বলেন, আমরা প্রশ্ন করলাম, হে আল্লাহর রাসূল (صلى الله عليه وسلم)! আপনার কি ধারণা, যে দিনটি এক বছরের সমান হবে, তাতে একদিনের নামাজ আদায় করলেই আমাদের জন্য যথেষ্ট হবে? তিনি বললেনঃ না, বরং তোমরা সেদিনের সঠিক অনুমান করে নেবে (এবং সে অনুযায়ী নামাজ আদায় করবে)। আমরা আবার প্রশ্ন করলাম, দুনিয়াতে তার চলার গতি কত দ্রুত হবে? তিনি বললেনঃ তার চলার গতি হবে বায়ুচালিত মেঘের অনুরূপ; তারপর সে কোন জাতির নিকট গিয়ে তাদেরকে নিজের দলের দিকে আহবান জানাবে, কিন্তু তারা তাকে মিথ্যাবাদী আখ্যায়িত করবে এবং তার দাবি প্রত্যাখ্যান করবে। সে তখন তাদের নিকট হতে ফিরে আসবে এবং তাদের ধন-সম্পদও তার পিছনে পিছনে চলে আসবে। তারা পরদিন সকালে নিজেদেরকে নিঃস্ব অবস্থায় পাবে। তারপর সে অন্য জাতির নিকট গিয়ে আহবান করবে। তারা তার আহবানে সাড়া দিবে এবং তাকে সত্য বলে মেনে নিবে। সে তখন আকাশকে বৃষ্টি বর্ষণের জন্য আদেশ করবে এবং সে অনুযায়ী আকাশ বৃষ্টি বর্ষণ করবে। তারপর সে যমীনকে ফসল উৎপাদনের জন্য নির্দেশ দিবে এবং সে মুতাবিক যমীন ফসল উৎপাদন করবে। তারপর বিকেলে তাদের পশুপালগুলো পূর্বের চেয়ে উঁচু কুঁজবিশিষ্ট মাংসবহুল নিতম্ববিশিষ্ট ও দুগ্ধপুষ্ট স্তনবিশিষ্ট হবে। তারপর সে নির্জন পতিত ভূমিতে গিয়ে বলবে, তোর ভিতরের খনিজভাণ্ডার বের করে দে। তারপর সে সেখান হতে ফিরে আসবে এবং সেখানকার ধনভাণ্ডার তার অনুসরণ করবে যেভাবে মৌমাছিরা রানী মৌমাছির অনুসরণ করে। তারপর সে পূর্ণযৌবন এক তরুণ যুবককে তার দিকে আহবান করবে। সে তলোয়ারের আঘাতে তাকে দুই টুকরা করে ফেলবে। তারপর সে তাকে ডাক দিবে, অমনি সে হাস্যোজ্জল চেহারা নিয়ে সামনে এসে দাঁড়াবে। এমতাবস্থায় এদিকে দামেস্কের পূর্ব প্রান্তের এক মসজিদের সাদা মিনারে হলুদ রংয়ের দুটি কাপড় পরিহিত অবস্থায় দুজন ফেরেশতার ডানায় ভর করে ঈসা ইবনু মারইয়াম (আঃ) অবতরণ করবেন। তিনি তাঁর মাথা নীচু করলে ফোঁটায় ফোঁটায় এবং উঁচু করলেও মণিমুক্তার ন্যায় (ঘাম) পড়তে থাকবে। তাঁর নিঃশ্বাস যে ব্যক্তিকেই স্পর্শ করবে সে মারা যাবে; আর তাঁর শ্বাসবায়ু দৃষ্টির শেষ সীমা পর্যন্ত পৌঁছবে। তারপর তিনি দাজ্জালকে খোঁজ করবেন এবং তাকে ‘লুদ্দ’-এর নগরদ্বারপ্রান্তে পেয়ে হত্যা করবেন। আল্লাহ তার নিকট ওহী প্রেরণ করবেনঃ “আমার বান্দাহদেরকে তূর পাহাড়ে সরিয়ে নাও। কেননা, আমি এমন একদল বান্দাহ অবতীর্ণ করছি যাদের বিরুদ্ধে যুদ্ধ করার ক্ষমতা কারো নেই।” তিনি বলেন, তারপর আল্লাহ ইয়াজুজ-মাজুজের দল পাঠাবেন। আল্লাহর বাণী অনুযায়ী তাদের অবস্থা হলো, “তারা প্রত্যেক উচ্চভূমি হতে ছুটে আসবে” (সূরা আম্বিয়া-৯৬)। তাদের প্রথম দলটি (সিরিয়ার) তাবারিয়া উপসাগর অতিক্রমকালে এর সমস্ত পানি পান করে শেষ করে ফেলবে। এদের শেষ দলটি এ স্থান দিয়ে অতিক্রমকালে বলবে, নিশ্চয়ই এই জলাশয়ে কোন সময় পানি ছিল। তারপর বাইতুল মাকদিসের পাহাড়ে পৌঁছার পর তাদের অভিযান সমাপ্ত হবে। তারা পরস্পর বলবে, আমরা তো দুনিয়ায় বসবাসকারীদের ধ্বংস করেছি, এবার চল আকাশে বসবাসকারীদের ধ্বংস করি। তারা এই বলে আকাশের দিকে তাদের তীর নিক্ষেপ করবে। আল্লাহ তাদের তীরসমূহ রক্তে রঞ্জিত করে ফেরত দিবেন। তারপর ঈসা ইবনু মারইয়াম (আঃ) তাঁর সাথীরা অবরুদ্ধ হয়ে পড়বেন। তারা (খাদ্যভাবে) এমন কঠিন পরিস্থিতিতে পতিত হবেন যে, তখন তাদের জন্য একটা গরুর মাথা তোমাদের এ যুগের একশত দিনারের চাইতে বেশি উত্তম মনে হবে। তারপর ঈসা (আঃ) ও তাঁর সাথীরা আল্লাহর দিকে রুজু হয়ে দোয়া করবেন। আল্লাহ তখন তাদের (ইয়াজুজ-মাজুজ বাহিনীর) ঘাড়ে মহামারীরূপে ‘নগফ’ নামক কীটের উৎপত্তি করবেন। তারপর তারা এমনভাবে ধ্বংস হয়ে যাবে যেন একটি প্রাণের মৃত্যু হয়েছে। তখন ঈসা (আঃ) তার সাথীদের নিয়ে (পাহাড় হতে) নেমে আসবেন। সেখানে তিনি এমন এক বিঘত পরিমাণ জায়গাও পাবেন না, যেখানে সেগুলোর পঁচা দুর্গন্ধময় রক্ত-মাংস ছড়িয়ে না থাকবে। তারপর তিনি সাথীদের নিয়ে আল্লাহর নিকট দোয়া করবেন। আল্লাহ তখন উটের ঘাড়ের ন্যায় লম্বা ঘাড়বিশিষ্ট এক প্রকার পাখি প্রেরণ করবেন। সেই পাখি ওদের লাশগুলো তুলে নিয়ে গভীর গর্তে নিক্ষেপ করবে। এদের পরিত্যক্ত তীর, ধনুক ও তূণীরগুলো মুসলিমগণ সাত বছর পর্যন্ত জ্বালানি হিসাবে ব্যবহার করবে। তারপর আল্লাহ এমন বৃষ্টি বর্ষণ করবেন যা সমস্ত ঘর-বাড়ি, স্থলভাগ ও কঠিন মাটির স্তরে গিয়ে পৌঁছবে এবং সমস্ত পৃথিবী ধুয়েমুছে আয়নার মতো ধকধকে হয়ে উঠবে। তারপর যমীনকে বলা হবে, তোর ফল ও ফসলসমূহ বের করে দে এবং বারকাত ও কল্যাণ ফিরিয়ে দে। তখন এরূপ পরিস্থিতি হবে যে, একদল লোকের জন্য একটি ডালিম পর্যাপ্ত হবে এবং একদল লোক এর খোসার ছায়াতলে আশ্রয় গ্রহণ করতে পারবে। দুধেও এরুপ বারকাত হবে যে, বিরাট একটি দলের জন্য একটি উটনীর দুধ, একটি গোত্রের জন্য একটি গাভীর দুধ এবং একটি ছোট দলের জন্য একটি ছাগলের দুধই যথেষ্ট হবে। এমতাবস্থায় কিছুদিন অতিক্রান্ত হওয়ার পর হঠাৎ আল্লাহ এমন এক বাতাস প্রেরণ করবেন যা সকল ঈমানদারের আত্মা ছিনিয়ে নেবে এবং অবশিষ্ট থাকবে শুধুমাত্র দুশ্চরিত্রের লোক যারা গাধার মতো প্রকাশ্যে নারী সম্ভোগে লিপ্ত হবে। তারপর তাদের উপর কেয়ামত সংঘটিত হবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا حُمَيْدُ بْنُ مَسْعَدَةَ، حَدَّثَنَا بِشْرُ بْنُ الْمُفَضَّلِ، عَنِ الْجُرَيْرِيِّ، عَنْ عَبْدِ الرَّحْمَنِ بْنِ أَبِي بَكْرَةَ، عَنْ أَبِيهِ، أَنَّ رَسُولَ اللَّهِ صلى الله عليه وسلم قَالَ ‏"‏ أَلاَ أُخْبِرُكُمْ بِأَكْبَرِ الْكَبَائِرِ ‏"‏ ‏.‏ قَالُوا بَلَى يَا رَسُولَ اللَّهِ ‏.‏ قَالَ ‏"‏ الإِشْرَاكُ بِاللَّهِ وَعُقُوقُ الْوَالِدَيْنِ وَشَهَادَةُ الزُّورِ أَوْ قَوْلُ الزُّورِ ‏"‏ ‏.‏ قَالَ فَمَا زَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم يَقُولُهَا حَتَّى قُلْنَا لَيْتَهُ سَكَتَ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏ وَفِي الْبَابِ عَنْ عَبْدِ اللَّهِ بْنِ عَمْرٍو ‏.‏</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন: আমি কি তোমাদেরকে সবচেয়ে মারাত্মক কবীরা গুনাহ প্রসঙ্গে জানিয়ে দেব না? সাহাবীগণ বলেন, অবশ্যই, ইয়া রাসূলুল্লাহ (صلى الله عليه وسلم)! তিনি বললেন: আল্লাহর সাথে শরীক করা, পিতা-মাতাকে কষ্ট দেওয়া ও তাদের অবাধ্য হওয়া এবং মিথ্যা সাক্ষ্য দেওয়া বা মিথ্যা কথা বলা। রাসূলুল্লাহ (صلى الله عليه وسلم) পুনঃপুনঃ এ কথাগুলো বলতে থাকলেন। আমরা (মনে মনে) বলতে লাগলাম, তিনি যদি চুপ করতেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا وَاصِلُ بْنُ عَبْدِ الأَعْلَى، حَدَّثَنَا مُحَمَّدُ بْنُ فُضَيْلٍ، عَنِ الأَعْمَشِ، عَنْ عَلِيِّ بْنِ مُدْرِكٍ، عَنْ هِلاَلِ بْنِ يِسَافٍ، عَنْ عِمْرَانَ بْنِ حُصَيْنِ، قَالَ سَمِعْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم يَقُولُ ‏ "‏ خَيْرُ النَّاسِ قَرْنِي ثُمَّ الَّذِينَ يَلُونَهُمْ ثُمَّ الَّذِينَ يَلُونَهُمْ ثُمَّ الَّذِينَ يَلُونَهُمْ ثَلاَثًا ثُمَّ يَجِيءُ قَوْمٌ مِنْ بَعْدِهِمْ يَتَسَمَّنُونَ وَيُحِبُّونَ السِّمَنَ يُعْطُونَ الشَّهَادَةَ قَبْلَ أَنْ يُسْأَلُوهَا ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَهَذَا حَدِيثٌ غَرِيبٌ مِنْ حَدِيثِ الأَعْمَشِ عَنْ عَلِيِّ بْنِ مُدْرِكٍ وَأَصْحَابُ الأَعْمَشِ إِنَّمَا رَوَوْا عَنِ الأَعْمَشِ عَنْ هِلاَلِ بْنِ يِسَافٍ عَنْ عِمْرَانَ بْنِ حُصَيْنٍ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم)-কে আমি বলতে শুনেছি: আমার যুগই (যুগের মানুষই) সর্বোত্তম, তারপর তাদের পরবর্তী যুগ, তারপর তাদের পরবর্তী যুগ (তিনবার বলেছেন)। তাদের পরবর্তী যুগে (তিন যুগ পরে) এমন সম্প্রদায়ের আবির্ভাব ঘটবে যারা হবে মোটা দেহবিশিষ্ট এবং তারা মোটা দেহবিশিষ্ট হওয়াটাই পছন্দ করবে। তারা সাক্ষ্য তলবের পূর্বেই সাক্ষ্য দিতে যাবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>عُمَرَ بْنِ الْخَطَّابِ عَنِ النَّبِيِّ صلى الله عليه وسلم قَالَ ‏"‏ خَيْرُ النَّاسِ قَرْنِي ثُمَّ الَّذِينَ يَلُونَهُمْ ثُمَّ الَّذِينَ يَلُونَهُمْ ثُمَّ يَفْشُو الْكَذِبُ حَتَّى يَشْهَدَ الرَّجُلُ وَلاَ يُسْتَشْهَدُ وَيَحْلِفُ الرَّجُلُ وَلاَ يُسْتَحْلَفُ ‏"‏ ‏.‏ وَمَعْنَى حَدِيثِ النَّبِيِّ صلى الله عليه وسلم ‏"‏ خَيْرُ الشُّهَدَاءِ الَّذِي يَأْتِي بِشَهَادَتِهِ قَبْلَ أَنْ يُسْأَلَهَا ‏"‏ ‏.‏ هُوَ عِنْدَنَا إِذَا أُشْهِدَ الرَّجُلُ عَلَى الشَّىْءِ أَنْ يُؤَدِّيَ شَهَادَتَهُ وَلاَ يَمْتَنِعَ مِنَ الشَّهَادَةِ هَكَذَا وَجْهُ الْحَدِيثِ عِنْدَ بَعْضِ أَهْلِ الْعِلْمِ ‏.‏ كَمُلَ وَالْحَمْدُ لِلَّهِ كِتَابُ الشَّهَادَاتِ وَيَلِيهِ كِتَابُ الزُّهْدِ</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم) বলেছেনঃ “আমার যুগ হচ্ছে সর্বোত্তম যুগ, তারপর তাদের পরবর্তী যুগ, তারপর তাদের পরবর্তী যুগ। তারপর এরূপভাবে মিথ্যার প্রসার ঘটবে যে, কারো নিকট সাক্ষ্য তলব না করা হলেও সে সাক্ষ্য দিবে, শপথ করতে বলা না হলেও শপথ করবে।”</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا بِشْرُ بْنُ هِلاَلٍ الصَّوَّافُ الْبَصْرِيُّ، حَدَّثَنَا جَعْفَرُ بْنُ سُلَيْمَانَ، عَنْ أَبِي طَارِقٍ، عَنِ الْحَسَنِ، عَنْ أَبِي هُرَيْرَةَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ مَنْ يَأْخُذُ عَنِّي هَؤُلاَءِ الْكَلِمَاتِ فَيَعْمَلُ بِهِنَّ أَوْ يُعَلِّمُ مَنْ يَعْمَلُ بِهِنَّ ‏"‏ ‏.‏ فَقَالَ أَبُو هُرَيْرَةَ فَقُلْتُ أَنَا يَا رَسُولَ اللَّهِ فَأَخَذَ بِيَدِي فَعَدَّ خَمْسًا وَقَالَ ‏"‏ اتَّقِ الْمَحَارِمَ تَكُنْ أَعْبَدَ النَّاسِ وَارْضَ بِمَا قَسَمَ اللَّهُ لَكَ تَكُنْ أَغْنَى النَّاسِ وَأَحْسِنْ إِلَى جَارِكَ تَكُنْ مُؤْمِنًا وَأَحِبَّ لِلنَّاسِ مَا تُحِبُّ لِنَفْسِكَ تَكُنْ مُسْلِمًا وَلاَ تُكْثِرِ الضَّحِكَ فَإِنَّ كَثْرَةَ الضَّحِكِ تُمِيتُ الْقَلْبَ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ غَرِيبٌ لاَ نَعْرِفُهُ إِلاَّ مِنْ حَدِيثِ جَعْفَرِ بْنِ سُلَيْمَانَ ‏.‏ وَالْحَسَنُ لَمْ يَسْمَعْ مِنْ أَبِي هُرَيْرَةَ شَيْئًا هَكَذَا رُوِيَ عَنْ أَيُّوبَ وَيُونُسَ بْنِ عُبَيْدٍ وَعَلِيِّ بْنِ زَيْدٍ قَالُوا لَمْ يَسْمَعِ الْحَسَنُ مِنْ أَبِي هُرَيْرَةَ ‏.‏ وَرَوَى أَبُو عُبَيْدَةَ النَّاجِيُّ عَنِ الْحَسَنِ هَذَا الْحَدِيثَ قَوْلَهُ وَلَمْ يَذْكُرْ فِيهِ عَنْ أَبِي هُرَيْرَةَ عَنِ النَّبِيِّ صلى الله عليه وسلم ‏.‏</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ এমন কে আছে যে আমার নিকট হতে এ কথাগুলো গ্রহণ করবে এবং সে মুতাবিক নিজেও আমল করবে অথবা এমন কাউকে শিক্ষা দিবে যে অনুরূপ আমল করবে? আবু হুরাইরা (রাঃ) বলেন, আমি বললাম, হে আল্লাহর রাসূল (صلى الله عليه وسلم)! আমি আছি। অতঃপর তিনি আমার হাত ধরলেন এবং গুনে গুনে এ পাঁচটি কথা বললেনঃ (১) তুমি হারামসমূহ হতে বিরত থাকলে লোকদের মধ্যে সর্বাপেক্ষা বড় আবিদ বলে গণ্য হবে; (২) তোমার ভাগ্যে আল্লাহ যা নির্ধারিত করে রেখেছেন তাতে খুশি থাকলে লোকদের মধ্যে সর্বাপেক্ষা স্বনির্ভর বলে গণ্য হবে; (৩) প্রতিবেশীর সাথে ভদ্র আচরণ করলে প্রকৃত মুমিন হতে পারবে; (৪) যা নিজের জন্য পছন্দ কর তা-ই অন্যের জন্য পছন্দ করতে পারলে প্রকৃত মুসলিম হতে পারবে এবং (৫) অধিক হাসা থেকে বিরত থাক। কেননা অতিরিক্ত হাস্য-কৌতুক হৃদয়কে মৃতবৎ করে দেয়।</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2306</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَبُو مُصْعَبٍ الْمَدَنِيُّ، عَنْ مُحَرَّرِ بْنِ هَارُونَ، عَنْ عَبْدِ الرَّحْمَنِ الأَعْرَجِ، عَنْ أَبِي هُرَيْرَةَ، أَنَّ رَسُولَ اللَّهِ صلى الله عليه وسلم قَالَ ‏ "‏ بَادِرُوا بِالأَعْمَالِ سَبْعًا هَلْ تَنْظُرُونَ إِلاَّ فَقْرًا مُنْسِيًا أَوْ غِنًى مُطْغِيًا أَوْ مَرَضًا مُفْسِدًا أَوْ هَرَمًا مُفَنِّدًا أَوْ مَوْتًا مُجْهِزًا أَوِ الدَّجَّالَ فَشَرُّ غَائِبٍ يُنْتَظَرُ أَوِ السَّاعَةَ فَالسَّاعَةُ أَدْهَى وَأَمَرُّ ‏"‏ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ لاَ نَعْرِفُهُ مِنْ حَدِيثِ الأَعْرَجِ عَنْ أَبِي هُرَيْرَةَ إِلاَّ مِنْ حَدِيثِ مُحَرَّرِ بْنِ هَارُونَ وَقَدْ رَوَى بِشْرُ بْنُ عُمَرَ وَغَيْرُهُ عَنْ مُحَرَّرِ بْنِ هَارُونَ هَذَا ‏.‏ وَقَدْ رَوَى مَعْمَرٌ هَذَا الْحَدِيثَ عَمَّنْ سَمِعَ سَعِيدًا الْمَقْبُرِيَّ عَنْ أَبِي هُرَيْرَةَ عَنِ النَّبِيِّ صلى الله عليه وسلم نَحْوَهُ ‏.‏ وَقَالَ تَنْتَظِرُونَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেন: তোমরা আমল করার ক্ষেত্রে সাতটি বিষয়ের অগ্রগামী হও। তোমরা কি এমন দারিদ্র্যের অপেক্ষায় আছ যা ভুলিয়ে দেয় অথবা এমন ধন-সম্পদের যা অবাধ্যতায় নিপতিত করে অথবা এমন রোগের যা নষ্ট করে দেয় অথবা নির্বোধ বানিয়ে দেয় বার্ধক্যের অথবা এমন মৃত্যুর যা হঠাৎ আসবে অথবা দাজ্জালের—একি অপেক্ষমাণ সবচেয়ে খারাপ অনিষ্ট অথবা কেয়ামতের? আর কেয়ামত তো আরো ভয়ঙ্কর, আরো তিক্ত।</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2307</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مَحْمُودُ بْنُ غَيْلاَنَ، حَدَّثَنَا الْفَضْلُ بْنُ مُوسَى، عَنْ مُحَمَّدِ بْنِ عَمْرٍو، عَنْ أَبِي سَلَمَةَ، عَنْ أَبِي هُرَيْرَةَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ أَكْثِرُوا ذِكْرَ هَاذِمِ اللَّذَّاتِ ‏"‏ ‏.‏ يَعْنِي الْمَوْتَ ‏.‏ قَالَ وَفِي الْبَابِ عَنْ أَبِي سَعِيدٍ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ তোমরা বেশি পরিমাণে জীবনের স্বাদ হরণকারীর অর্থাৎ মৃত্যুর স্মরণ কর।</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا هَنَّادٌ، حَدَّثَنَا يَحْيَى بْنُ مَعِينٍ، حَدَّثَنَا هِشَامُ بْنُ يُوسُفَ، حَدَّثَنِي عَبْدُ اللَّهِ بْنُ بَحِيرٍ، أَنَّهُ سَمِعَ هَانِئًا، مَوْلَى عُثْمَانَ قَالَ كَانَ عُثْمَانُ إِذَا وَقَفَ عَلَى قَبْرٍ بَكَى حَتَّى يَبُلَّ لِحْيَتَهُ فَقِيلَ لَهُ تُذْكَرُ الْجَنَّةُ وَالنَّارُ فَلاَ تَبْكِي وَتَبْكِي مِنْ هَذَا فَقَالَ إِنَّ رَسُولَ اللَّهِ صلى الله عليه وسلم قَالَ ‏"‏ إِنَّ الْقَبْرَ أَوَّلُ مَنَازِلِ الآخِرَةِ فَإِنْ نَجَا مِنْهُ فَمَا بَعْدَهُ أَيْسَرُ مِنْهُ وَإِنْ لَمْ يَنْجُ مِنْهُ فَمَا بَعْدَهُ أَشَدُّ مِنْهُ ‏"‏ ‏.‏ قَالَ وَقَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ مَا رَأَيْتُ مَنْظَرًا قَطُّ إِلاَّ وَالْقَبْرُ أَفْظَعُ مِنْهُ ‏"‏ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ لاَ نَعْرِفُهُ إِلاَّ مِنْ حَدِيثِ هِشَامِ بْنِ يُوسُفَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>উসমান (রাঃ) কোন কবরের পাশে দাঁড়িয়ে এত কাঁদতেন যে, তার দাড়ি ভিজে যেত। তাকে প্রশ্ন করা হলো, জান্নাত-জাহান্নামের আলোচনা করা হলে তো আপনি কাঁদেন না, অথচ এই কবর দর্শনে এত বেশি কাঁদেন কেন? তিনি বললেন, রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ আখিরাতের মনযিলসমূহের (প্রাসাদ) মধ্যে কবর হলো প্রথম মনযিল। এখান হতে কেউ মুক্তি পেয়ে গেলে তবে তার জন্য পরবর্তী মনযিলগুলোতে মুক্তি পাওয়া খুব সহজ হয়ে যাবে। আর সে এখান হতে মুক্তি না পেলে তবে তার জন্য পরবর্তী মনযিলগুলো আরো বেশি কঠিন হবে। তিনি (রাঃ) বলেন, রাসূলুল্লাহ (صلى الله عليه وسلم) আরো বলেছেনঃ আমি কবরের দৃশ্যের চাইতে অধিক ভয়ংকর দৃশ্য আর কখনো দেখিনি।</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2309</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مَحْمُودُ بْنُ غَيْلاَنَ، حَدَّثَنَا أَبُو دَاوُدَ، أَخْبَرَنَا شُعْبَةُ، عَنْ قَتَادَةَ، قَالَ سَمِعْتُ أَنَسًا، يُحَدِّثُ عَنْ عُبَادَةَ بْنِ الصَّامِتِ، عَنِ النَّبِيِّ صلى الله عليه وسلم قَالَ ‏ "‏ مَنْ أَحَبَّ لِقَاءَ اللَّهِ أَحَبَّ اللَّهُ لِقَاءَهُ وَمَنْ كَرِهَ لِقَاءَ اللَّهِ كَرِهَ اللَّهُ لِقَاءَهُ ‏"‏ ‏.‏ قَالَ وَفِي الْبَابِ عَنْ أَبِي هُرَيْرَةَ وَعَائِشَةَ وَأَنَسٍ وَأَبِي مُوسَى ‏.‏ قَالَ حَدِيثُ عُبَادَةَ حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>নবী (صلى الله عليه وسلم) বলেছেনঃ আল্লাহ তা’আলার সাথে সাক্ষাৎ করাকে যে লোক পছন্দ করে, তার সাথে সাক্ষাৎ করতে আল্লাহ তা’আলাও পছন্দ করেন। আর আল্লাহ তা’আলার সাথে সাক্ষাৎ করতে যে লোক অপছন্দ করে, আল্লাহ তা’আলাও তার সাথে সাক্ষাৎ করতে অপছন্দ করেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَبُو الأَشْعَثِ، أَحْمَدُ بْنُ الْمِقْدَامِ الْعِجْلِيُّ حَدَّثَنَا مُحَمَّدُ بْنُ عَبْدِ الرَّحْمَنِ الطُّفَاوِيُّ، حَدَّثَنَا هِشَامُ بْنُ عُرْوَةَ، عَنْ أَبِيهِ، عَنْ عَائِشَةَ، قَالَتْ لَمَّا نَزَلَتْ هَذِهِ الآيَةُ ‏:‏ ‏(‏ وَأَنْذِرْ عَشِيرَتَكَ الأَقْرَبِينَ ‏)‏ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ يَا صَفِيَّةُ بِنْتَ عَبْدِ الْمُطَّلِبِ يَا فَاطِمَةُ بِنْتَ مُحَمَّدٍ يَا بَنِي عَبْدِ الْمُطَّلِبِ إِنِّي لاَ أَمْلِكُ لَكُمْ مِنَ اللَّهِ شَيْئًا سَلُونِي مِنْ مَالِي مَا شِئْتُمْ ‏"‏ ‏.‏ قَالَ وَفِي الْبَابِ عَنْ أَبِي هُرَيْرَةَ وَأَبِي مُوسَى وَابْنِ عَبَّاسٍ ‏.‏ قَالَ حَدِيثُ عَائِشَةَ حَدِيثٌ حَسَنٌ غَرِيبٌ ‏.‏ هَكَذَا رَوَى بَعْضُهُمْ عَنْ هِشَامِ بْنِ عُرْوَةَ نَحْوَ هَذَا وَرَوَى بَعْضُهُمْ عَنْ هِشَامٍ عَنْ أَبِيهِ عَنِ النَّبِيِّ صلى الله عليه وسلم مُرْسَلاً لَمْ يَذْكُرْ فِيهِ عَنْ عَائِشَةَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>যখন এ আয়াত অবতীর্ণ হলো : “আপনি আপনার নিকটাত্মীয়দের ভয় প্রদর্শন করুন” (২৬ : ২১৪), তখন রাসূলুল্লাহ (صلى الله عليه وسلم) বললেন, “হে সাফিয়া বিনত আবদুল মুত্তালিব, হে ফাতিমা বিনত মুহাম্মাদ, হে আবদুল মুত্তালিবের বংশধর! আল্লাহর (পাকড়াও) হতে তোমাদেরকে বাঁচানোর ক্ষমতা আমার নেই। আমার ধন-সম্পদ হতে তোমরা যতটুকু খুশি চাইতে পার (কিতাবুল তাফসীরে পুনরুক্ত)।”</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا هَنَّادٌ، حَدَّثَنَا عَبْدُ اللَّهِ بْنُ الْمُبَارَكِ، عَنْ عَبْدِ الرَّحْمَنِ بْنِ عَبْدِ اللَّهِ الْمَسْعُودِيِّ، عَنْ مُحَمَّدِ بْنِ عَبْدِ الرَّحْمَنِ، عَنْ عِيسَى بْنِ طَلْحَةَ، عَنْ أَبِي هُرَيْرَةَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ لاَ يَلِجُ النَّارَ رَجُلٌ بَكَى مِنْ خَشْيَةِ اللَّهِ حَتَّى يَعُودَ اللَّبَنُ فِي الضَّرْعِ وَلاَ يَجْتَمِعُ غُبَارٌ فِي سَبِيلِ اللَّهِ وَدُخَانُ جَهَنَّمَ ‏"‏ ‏.‏ قَالَ وَفِي الْبَابِ عَنْ أَبِي رَيْحَانَةَ وَابْنِ عَبَّاسٍ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏ وَمُحَمَّدُ بْنُ عَبْدِ الرَّحْمَنِ هُوَ مَوْلَى آلِ طَلْحَةَ وَهُوَ مَدَنِيٌّ ثِقَةٌ رَوَى عَنْهُ شُعْبَةُ وَسُفْيَانُ الثَّوْرِيُّ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন: আল্লাহর ভয়ে ক্রন্দনকারী ব্যক্তি জাহান্নামে প্রবেশ করবে না, যেরূপ দোহনকৃত দুধ আবার স্তনে ফিরিয়ে নেয়া যায় না। আর আল্লাহর পথের (জিহাদের) ধুলা ও জাহান্নামের ধোঁয়া কখনো একত্র হবে না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2312</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَحْمَدُ بْنُ مَنِيعٍ، حَدَّثَنَا أَبُو أَحْمَدَ الزُّبَيْرِيُّ، حَدَّثَنَا إِسْرَائِيلُ، عَنْ إِبْرَاهِيمَ بْنِ الْمُهَاجِرِ، عَنْ مُجَاهِدٍ، عَنْ مُوَرِّقٍ، عَنْ أَبِي ذَرٍّ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ إِنِّي أَرَى مَا لاَ تَرَوْنَ وَأَسْمَعُ مَا لاَ تَسْمَعُونَ أَطَّتِ السَّمَاءُ وَحُقَّ لَهَا أَنْ تَئِطَّ مَا فِيهَا مَوْضِعُ أَرْبَعِ أَصَابِعَ إِلاَّ وَمَلَكٌ وَاضِعٌ جَبْهَتَهُ سَاجِدًا لِلَّهِ لَوْ تَعْلَمُونَ مَا أَعْلَمُ لَضَحِكْتُمْ قَلِيلاً وَلَبَكَيْتُمْ كَثِيرًا وَمَا تَلَذَّذْتُمْ بِالنِّسَاءِ عَلَى الْفُرُشِ وَلَخَرَجْتُمْ إِلَى الصُّعُدَاتِ تَجْأَرُونَ إِلَى اللَّهِ ‏"‏ ‏.‏ لَوَدِدْتُ أَنِّي كُنْتُ شَجَرَةً تُعْضَدُ ‏.‏ قَالَ أَبُو عِيسَى وَفِي الْبَابِ عَنْ أَبِي هُرَيْرَةَ وَعَائِشَةَ وَابْنِ عَبَّاسٍ وَأَنَسٍ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ ‏.‏ وَيُرْوَى مِنْ غَيْرِ هَذَا الْوَجْهِ أَنَّ أَبَا ذَرٍّ قَالَ لَوَدِدْتُ أَنِّي كُنْتُ شَجَرَةً تُعْضَدُ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ আমি (অদৃশ্য জগতের) যা দেখি তোমরা তা দেখ না, আর আমি যা শুনতে পাই তোমরা তা শুনতে পাও না। আসমান তো চড়চড় শব্দ করছে, আর সে এই শব্দ করার যোগ্য। তাতে এমন চার আঙুল পরিমাণ জায়গাও নেই যেখানে কোন ফেরেশতা আল্লাহর জন্যে অবনত মস্তকে সিজদায় পড়ে না আছে। আল্লাহর শপথ! আমি যা জানি তোমরা যদি তা জানতে তাহলে তোমরা খুব কমই হাসতে, বেশি কাঁদতে এবং বিছানায় স্ত্রীদের উপভোগ করতে না, বাড়ি-ঘর ছেড়ে পথে-প্রান্তরে বেরিয়ে পড়তে, আল্লাহর সামনে কাকুতি-মিনতি করতে। বর্ণনাকারী বলেন, আমার মন চায় আমি যদি একটি বৃক্ষ হতাম আর তা কেটে ফেলা হতো।</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَبُو حَفْصٍ، عَمْرُو بْنُ عَلِيٍّ الْفَلاَّسُ حَدَّثَنَا عَبْدُ الْوَهَّابِ الثَّقَفِيُّ، عَنْ مُحَمَّدِ بْنِ عَمْرٍو، عَنْ أَبِي سَلَمَةَ، عَنْ أَبِي هُرَيْرَةَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ لَوْ تَعْلَمُونَ مَا أَعْلَمُ لَضَحِكْتُمْ قَلِيلاً وَلَبَكَيْتُمْ كَثِيرًا ‏"‏ ‏.‏ هَذَا حَدِيثٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ আমি যা জানি তোমরা যদি তা জানতে, তাহলে খুব অল্পই হাসতে এবং খুব বেশি কাঁদতে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2314</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ بَشَّارٍ، حَدَّثَنَا ابْنُ أَبِي عَدِيٍّ، عَنْ مُحَمَّدِ بْنِ إِسْحَاقَ، حَدَّثَنِي مُحَمَّدُ بْنُ إِبْرَاهِيمَ، عَنْ عِيسَى بْنِ طَلْحَةَ، عَنْ أَبِي هُرَيْرَةَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ إِنَّ الرَّجُلَ لَيَتَكَلَّمُ بِالْكَلِمَةِ لاَ يَرَى بِهَا بَأْسًا يَهْوِي بِهَا سَبْعِينَ خَرِيفًا فِي النَّارِ ‏"‏ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ مِنْ هَذَا الْوَجْهِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ যে লোক এমন কথাও বলে যে প্রসঙ্গে সে মনে করে যে, তাতে কোনও অসুবিধা নেই, এইজন্য সে সত্তর বছর জাহান্নামে অবস্থান করবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ بَشَّارٍ، حَدَّثَنَا يَحْيَى بْنُ سَعِيدٍ، حَدَّثَنَا بَهْزُ بْنُ حَكِيمٍ، حَدَّثَنِي أَبِي، عَنْ جَدِّي، قَالَ سَمِعْتُ النَّبِيَّ صلى الله عليه وسلم يَقُولُ ‏ "‏ وَيْلٌ لِلَّذِي يُحَدِّثُ بِالْحَدِيثِ لِيُضْحِكَ بِهِ الْقَوْمَ فَيَكْذِبُ وَيْلٌ لَهُ وَيْلٌ لَهُ ‏"‏ ‏.‏ قَالَ وَفِي الْبَابِ عَنْ أَبِي هُرَيْرَةَ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>তার দাদা বলেন, রাসূলুল্লাহ (صلى الله عليه وسلم)-কে আমি বলতে শুনেছি : সেই লোক ধ্বংস হোক যে মানুষদের হাসানোর উদ্দেশ্যে কথা বলতে গিয়ে মিথ্যা বলে। সে নিপাত যাক, সে নিপাত যাক।</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2316</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا سُلَيْمَانُ بْنُ عَبْدِ الْجَبَّارِ الْبَغْدَادِيُّ، حَدَّثَنَاَ عُمَرُ بْنُ حَفْصِ بْنِ غِيَاثٍ، حَدَّثَنَا أَبِي، عَنِ الأَعْمَشِ، عَنْ أَنَسِ بْنِ مَالِكٍ، قَالَ تُوُفِّيَ رَجُلٌ مِنْ أَصْحَابِهِ فَقَالَ يَعْنِي رَجُلٌ أَبْشِرْ بِالْجَنَّةِ ‏.‏ فَقَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ أَوَلاَ تَدْرِي فَلَعَلَّهُ تَكَلَّمَ فِيمَا لاَ يَعْنِيهِ أَوْ بَخِلَ بِمَا لاَ يَنْقُصُهُ ‏"‏ ‏.‏ قَالَ هَذَا حَدِيثٌ غَرِيبٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>কোন এক সময় রাসূলুল্লাহ (صلى الله عليه وسلم)-এর এক সাহাবী মারা গেলে এক ব্যক্তি বলল, জান্নাতের সুসংবাদ গ্রহণ কর। তখন রাসূলুল্লাহ (صلى الله عليه وسلم) বললেন: তুমি তো জান না, হয়ত সে বেহুদা কথা বলেছে অথবা যা দান করলে তার কোন ক্ষতি হত না তাতেও সে কৃপণতা করেছে?</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَحْمَدُ بْنُ نَصْرٍ النَّيْسَابُورِيُّ، وَغَيْرُ، وَاحِدٍ، قَالُوا حَدَّثَنَا أَبُو مُسْهِرٍ، عَنْ إِسْمَاعِيلَ بْنِ عَبْدِ اللَّهِ بْنِ سَمَاعَةَ، عَنِ الأَوْزَاعِيِّ، عَنْ قُرَّةَ، عَنِ الزُّهْرِيِّ، عَنْ أَبِي سَلَمَةَ، عَنْ أَبِي هُرَيْرَةَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ مِنْ حُسْنِ إِسْلاَمِ الْمَرْءِ تَرْكُهُ مَا لاَ يَعْنِيهِ ‏"‏ ‏.‏ قَالَ هَذَا حَدِيثٌ غَرِيبٌ لاَ نَعْرِفُهُ مِنْ حَدِيثِ أَبِي سَلَمَةَ عَنْ أَبِي هُرَيْرَةَ عَنِ النَّبِيِّ صلى الله عليه وسلم إِلاَّ مِنْ هَذَا الْوَجْهِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ কোন ব্যক্তির ইসলামের অন্যতম সৌন্দর্য হলো অনর্থক আচরণ ত্যাগ করা।</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2318</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا قُتَيْبَةُ، حَدَّثَنَا مَالِكُ بْنُ أَنَسٍ، عَنِ الزُّهْرِيِّ، عَنْ عَلِيِّ بْنِ حُسَيْنٍ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ إِنَّ مِنْ حُسْنِ إِسْلاَمِ الْمَرْءِ تَرْكَهُ مَا لاَ يَعْنِيهِ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى وَهَكَذَا رَوَى غَيْرُ وَاحِدٍ مِنْ أَصْحَابِ الزُّهْرِيِّ عَنِ الزُّهْرِيِّ عَنْ عَلِيِّ بْنِ حُسَيْنٍ عَنِ النَّبِيِّ صلى الله عليه وسلم نَحْوَ حَدِيثِ مَالِكٍ مُرْسَلاً وَهَذَا عِنْدَنَا أَصَحُّ مِنْ حَدِيثِ أَبِي سَلَمَةَ عَنْ أَبِي هُرَيْرَةَ ‏.‏ وَعَلِيُّ بْنُ حُسَيْنٍ لَمْ يُدْرِكْ عَلِيَّ بْنَ أَبِي طَالِبٍ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ কোন ব্যক্তির ইসলামের অন্যতম সৌন্দর্য হলো অর্থহীন কথা বা কাজ ত্যাগ করা। পূর্বের হাদিসের সহায়তায় সহিহ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا هَنَّادٌ، حَدَّثَنَا عَبْدَةُ، عَنْ مُحَمَّدِ بْنِ عَمْرٍو، حَدَّثَنِي أَبِي، عَنْ جَدِّي، قَالَ سَمِعْتُ بِلاَلَ بْنَ الْحَارِثِ الْمُزَنِيَّ، صَاحِبَ رَسُولِ اللَّهِ صلى الله عليه وسلم يَقُولُ سَمِعْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم يَقُولُ ‏ "‏ إِنَّ أَحَدَكُمْ لَيَتَكَلَّمُ بِالْكَلِمَةِ مِنْ رِضْوَانِ اللَّهِ مَا يَظُنُّ أَنْ تَبْلُغَ مَا بَلَغَتْ فَيَكْتُبُ اللَّهُ لَهُ بِهَا رِضْوَانَهُ إِلَى يَوْمِ يَلْقَاهُ وَإِنَّ أَحَدَكُمْ لَيَتَكَلَّمُ بِالْكَلِمَةِ مِنْ سَخَطِ اللَّهِ مَا يَظُنُّ أَنْ تَبْلُغَ مَا بَلَغَتْ فَيَكْتُبُ اللَّهُ عَلَيْهِ بِهَا سَخَطَهُ إِلَى يَوْمِ يَلْقَاهُ ‏"‏ ‏.‏ قَالَ وَفِي الْبَابِ عَنْ أُمِّ حَبِيبَةَ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏ وَهَكَذَا رَوَاهُ غَيْرُ وَاحِدٍ عَنْ مُحَمَّدِ بْنِ عَمْرٍو نَحْوَ هَذَا قَالُوا عَنْ مُحَمَّدِ بْنِ عَمْرٍو عَنْ أَبِيهِ عَنْ جَدِّهِ عَنْ بِلاَلِ بْنِ الْحَارِثِ ‏.‏ وَرَوَى هَذَا الْحَدِيثَ مَالِكٌ عَنْ مُحَمَّدِ بْنِ عَمْرٍو عَنْ أَبِيهِ عَنْ بِلاَلِ بْنِ الْحَارِثِ وَلَمْ يَذْكُرْ فِيهِ عَنْ جَدِّهِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>আমি রাসূলুল্লাহ (صلى الله عليه وسلم)-কে বলতে শুনেছি : তোমাদের মধ্যে কোন ব্যক্তি কখনো আল্লাহ তা’আলার সন্তুষ্টির কথা বলে, যার সম্পর্কে সে ধারণাও করে না যে, তা কোথায় গিয়ে পৌঁছবে, অথচ আল্লাহ তা’আলা তার এ কথার কারণে তাঁর সাথে মিলিত হওয়ার দিন পর্যন্ত তার জন্য স্বীয় সন্তুষ্টি লিখে দেন। আবার তোমাদের মধ্যে কোন ব্যক্তি কখনো আল্লাহ তা’আলার অসন্তুষ্টির কথা বলে, যার সম্পর্কে সে চিন্তাও করে না যে, তা কোন পর্যন্ত গিয়ে পৌঁছবে। অথচ এ কথার কারণে আল্লাহ তা’আলা তার সাথে মিলিত হওয়ার দিন পর্যন্ত তার জন্য অসন্তুষ্টি লিখে দেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا قُتَيْبَةُ، حَدَّثَنَا عَبْدُ الْحَمِيدِ بْنُ سُلَيْمَانَ، عَنْ أَبِي حَازِمٍ، عَنْ سَهْلِ بْنِ سَعْدٍ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ لَوْ كَانَتِ الدُّنْيَا تَعْدِلُ عِنْدَ اللَّهِ جَنَاحَ بَعُوضَةٍ مَا سَقَى كَافِرًا مِنْهَا شَرْبَةَ مَاءٍ ‏"‏ ‏.‏ وَفِي الْبَابِ عَنْ أَبِي هُرَيْرَةَ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ صَحِيحٌ غَرِيبٌ مِنْ هَذَا الْوَجْهِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন: আল্লাহর নিকট যদি এই পৃথিবীর মূল্য মশার একটি পাখার সমান হতো তাহলে তিনি কোনো কাফিরকে এখানকার পানির এক ঢোকও পান করাতেন না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>3699</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَبْدُ اللَّهِ بْنُ عَبْدِ الرَّحْمَنِ، أَخْبَرَنَا عَبْدُ اللَّهِ بْنُ جَعْفَرٍ الرَّقِّيُّ، حَدَّثَنَا عُبَيْدُ اللَّهِ بْنُ عَمْرٍو، عَنْ زَيْدٍ، هُوَ ابْنُ أَبِي أُنَيْسَةَ عَنْ أَبِي إِسْحَاقَ، عَنْ أَبِي عَبْدِ الرَّحْمَنِ السُّلَمِيِّ، قَالَ لَمَّا حُصِرَ عُثْمَانُ أَشْرَفَ عَلَيْهِمْ فَوْقَ دَارِهِ ثُمَّ قَالَ أُذَكِّرُكُمْ بِاللَّهِ هَلْ تَعْلَمُونَ أَنَّ حِرَاءَ حِينَ انْتَفَضَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏"‏ اثْبُتْ حِرَاءُ فَلَيْسَ عَلَيْكَ إِلاَّ نَبِيٌّ أَوْ صِدِّيقٌ أَوْ شَهِيدٌ ‏"‏ ‏.‏ قَالُوا نَعَمْ ‏.‏ قَالَ أُذَكِّرُكُمْ بِاللَّهِ هَلْ تَعْلَمُونَ أَنَّ رَسُولَ اللَّهِ صلى الله عليه وسلم قَالَ فِي جَيْشِ الْعُسْرَةِ ‏"‏ مَنْ يُنْفِقُ نَفَقَةً مُتَقَبَّلَةً ‏"‏ ‏.‏ وَالنَّاسُ مُجْهَدُونَ مُعْسِرُونَ فَجَهَّزْتُ ذَلِكَ الْجَيْشَ قَالُوا نَعَمْ ‏.‏ ثُمَّ قَالَ أُذَكِّرُكُمْ بِاللَّهِ هَلْ تَعْلَمُونَ أَنَّ بِئْرَ رُومَةَ لَمْ يَكُنْ يَشْرَبُ مِنْهَا أَحَدٌ إِلاَّ بِثَمَنٍ فَابْتَعْتُهَا فَجَعَلْتُهَا لِلْغَنِيِّ وَالْفَقِيرِ وَابْنِ السَّبِيلِ قَالُوا اللَّهُمَّ نَعَمْ وَأَشْيَاءُ عَدَّدَهَا ‏.‏ هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ غَرِيبٌ مِنْ هَذَا الْوَجْهِ مِنْ حَدِيثِ أَبِي عَبْدِ الرَّحْمَنِ السُّلَمِيِّ عَنْ عُثْمَانَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>যখন উসমান (রাঃ) বিদ্রোহীদের মাধ্যমে অবরুদ্ধ হয়ে পড়েন, সে সময় তিনি তার ঘরের উপরিতলে (ছাদে) উঠলেন, তারপর বললেন, আজ আল্লাহর কসম করে আমি তোমাদের মনে করিয়ে দিচ্ছি, তোমরা কি অবহিত আছ যে, হেরা পর্বত কম্পিত হলে রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছিলেনঃ হে হেরা! শান্ত হয়ে যাও, কেননা তোমার উপর রয়েছেন একজন নবী কিংবা একজন সিদ্দীক কিংবা একজন শহীদ? লোকেরা বলল, হ্যাঁ। তিনি পুনরায় বললেন, আমি আল্লাহ (صلى الله عليه وسلم) তা’আলার নামে কসম করে তোমাদেরকে মনে করিয়ে দিচ্ছি যে, রাসূলুল্লাহ (صلى الله عليه وسلم) উসরা বাহিনীর (তাবূকের যুদ্ধের) জন্য বলেছিলেনঃ কে এটা পছন্দনীয় বা কবুল হওয়ার যোগ্য (অধিক পরিমাণের) খরচ দিতে তৈরী আছে? সে সময় লোকেরা চরম আর্থিক সংকট ও কঠিন পরিস্থিতির মুকাবিলা করছিল। অতএব সেই বাহিনীর প্রয়োজনীয় ব্যয় আমিই বহন করেছি। লোকেরা বলল, হ্যাঁ। আবার তিনি বললেন, আল্লাহ তা’আলার নামে প্রতিজ্ঞা করে তোমাদেরকে আমি আরও মনে করিয়ে দিতে চাই, তোমরা কি জ্ঞাত আছ যে, রুমা কূপের পানি কেউই ক্রয় করা ব্যতীত পান করতে পারত না? সেই কূপ আমি ক্রয় করে আমি ধনী, দরিদ্র ও মুসাফিরদের জন্য ওয়াকফ করে দিয়েছি। লোকেরা বলল, ইয়া আল্লাহ! হ্যাঁ (আমরা জানি)। তিনি তার আরো কিছু (জনহিতকর) সমাজকল্যাণমূলক কথা মনে করিয়ে দেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ بَشَّارٍ، حَدَّثَنَا أَبُو دَاوُدَ، حَدَّثَنَا السَّكَنُ بْنُ الْمُغِيرَةِ، وَيُكْنَى أَبَا مُحَمَّدٍ، مَوْلًى لآلِ عُثْمَانَ حَدَّثَنَا الْوَلِيدُ بْنُ أَبِي هِشَامٍ، عَنْ فَرْقَدٍ أَبِي طَلْحَةَ، عَنْ عَبْدِ الرَّحْمَنِ بْنِ خَبَّابٍ، قَالَ شَهِدْتُ النَّبِيَّ صلى الله عليه وسلم وَهُوَ يَحُثُّ عَلَى جَيْشِ الْعُسْرَةِ فَقَامَ عُثْمَانُ بْنُ عَفَّانَ فَقَالَ يَا رَسُولَ اللَّهِ عَلَىَّ مِائَةُ بَعِيرٍ بِأَحْلاَسِهَا وَأَقْتَابِهَا فِي سَبِيلِ اللَّهِ ‏.‏ ثُمَّ حَضَّ عَلَى الْجَيْشِ فَقَامَ عُثْمَانُ بْنُ عَفَّانَ فَقَالَ يَا رَسُولَ اللَّهِ عَلَىَّ مِائَتَا بَعِيرٍ بِأَحْلاَسِهَا وَأَقْتَابِهَا فِي سَبِيلِ اللَّهِ ‏.‏ ثُمَّ حَضَّ عَلَى الْجَيْشِ فَقَامَ عُثْمَانُ بْنُ عَفَّانَ فَقَالَ يَا رَسُولَ اللَّهِ لِلَّهِ عَلَىَّ ثَلاَثُمِائَةِ بَعِيرٍ بِأَحْلاَسِهَا وَأَقْتَابِهَا فِي سَبِيلِ اللَّهِ ‏.‏ فَأَنَا رَأَيْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم يَنْزِلُ عَنِ الْمِنْبَرِ وَهُوَ يَقُولُ ‏ "‏ مَا عَلَى عُثْمَانَ مَا عَمِلَ بَعْدَ هَذِهِ مَا عَلَى عُثْمَانَ مَا عَمِلَ بَعْدَ هَذِهِ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ غَرِيبٌ مِنْ هَذَا الْوَجْهِ لاَ نَعْرِفُهُ إِلاَّ مِنْ حَدِيثِ السَّكَنِ بْنِ الْمُغِيرَةِ ‏.‏ وَفِي الْبَابِ عَنْ عَبْدِ الرَّحْمَنِ بْنِ سَمُرَةَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>যখন রাসূলুল্লাহ (صلى الله عليه وسلم) জনসাধারণকে জাইশুল উসরাত অর্থাৎ তাবুকের সামরিক অভিযানে আর্থিক সহায়তা দেবার জন্য উৎসাহিত করছিলেন, তখন আমি সেখানে হাজির ছিলাম। উসমান (রাঃ) দাঁড়িয়ে বললেনঃ হে আল্লাহর রাসূল! আমি সুসজ্জিত এক শত উট (গদি-পালানসহ) আল্লাহর রাস্তায় দান করলাম। রাসূলুল্লাহ (صلى الله عليه وسلم) আবার যুদ্ধের (আর্থিক খরচ বহনের উদ্দেশ্যে) লোকদেরকে উৎসাহিত করলেন। উসমান (রাঃ) দাঁড়িয়ে বললেন, হে আল্লাহর রাসূল! গদি-পালানসহ আমি দুই শত উট আল্লাহর রাস্তায় দান করলাম। তিনি আবারও লোকদেরকে যুদ্ধের জন্য উৎসাহিত করেন। উসমান (রাঃ) দাঁড়িয়ে বললেনঃ হে আল্লাহর রাসূল! আমি গদি-পালানসহ তিন শত উট আল্লাহর রাস্তায় দান করলাম। রাবী আবদুর রহমান (রাঃ) বলেনঃ আমি রাসূলুল্লাহ (صلى الله عليه وسلم)-কে মিম্বারের উপর হতে এ কথা বলতে বলতে নামতে দেখছি- আজকের পর হতে উসমান যাই করুক তার জন্য তাকে কৈফিয়ত দিতে হবে না। আজকের পর হতে উসমান যাই করুক তার জন্য তাকে কৈফিয়ত দিতে হবে না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>3764</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ بَشَّارٍ، حَدَّثَنَا عَبْدُ الْوَهَّابِ الثَّقَفِيُّ، حَدَّثَنَا خَالِدٌ الْحَذَّاءُ، عَنْ عِكْرِمَةَ، عَنْ أَبِي هُرَيْرَةَ، قَالَ مَا احْتَذَى النِّعَالَ وَلاَ انْتَعَلَ وَلاَ رَكِبَ الْمَطَايَا وَلاَ رَكِبَ الْكُورَ بَعْدَ رَسُولِ اللَّهِ صلى الله عليه وسلم أَفْضَلُ مِنْ جَعْفَرِ بْنِ أَبِي طَالِبٍ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ غَرِيبٌ ‏.‏ وَالْكُورُ الرَّحْلُ</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم)-এর পর জাফর (রাঃ)-এর চেয়ে উত্তম কোন লোক জুতা পরিধান করেনি, জন্তুযানে আরোহণ করেনি, উটের হাওদায় উঠেনি।</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَبُو سَعِيدٍ الأَشَجُّ، حَدَّثَنَا إِسْمَاعِيلُ بْنُ إِبْرَاهِيمَ أَبُو يَحْيَى التَّيْمِيُّ، حَدَّثَنَا إِبْرَاهِيمُ أَبُو إِسْحَاقَ الْمَخْزُومِيُّ، عَنْ سَعِيدٍ الْمَقْبُرِيِّ، عَنْ أَبِي هُرَيْرَةَ، قَالَ إِنْ كُنْتُ لأَسْأَلُ الرَّجُلَ مِنْ أَصْحَابِ النَّبِيِّ صلى الله عليه وسلم عَنِ الآيَاتِ مِنَ الْقُرْآنِ أَنَا أَعْلَمُ بِهَا مِنْهُ مَا أَسْأَلُهُ إِلاَّ لِيُطْعِمَنِي شَيْئًا فَكُنْتُ إِذَا سَأَلْتُ جَعْفَرَ بْنَ أَبِي طَالِبٍ لَمْ يُجِبْنِي حَتَّى يَذْهَبَ بِي إِلَى مَنْزِلِهِ فَيَقُولُ لاِمْرَأَتِهِ يَا أَسْمَاءُ أَطْعِمِينَا شَيْئًا ‏.‏ فَإِذَا أَطْعَمَتْنَا أَجَابَنِي وَكَانَ جَعْفَرٌ يُحِبُّ الْمَسَاكِينَ وَيَجْلِسُ إِلَيْهِمْ وَيُحَدِّثُهُمْ وَيُحَدِّثُونَهُ فَكَانَ رَسُولُ اللَّهِ صلى الله عليه وسلم يَكْنِيهِ بِأَبِي الْمَسَاكِينِ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ غَرِيبٌ ‏.‏ وَأَبُو إِسْحَاقَ الْمَخْزُومِيُّ هُوَ إِبْرَاهِيمُ بْنُ الْفَضْلِ الْمَدَنِيُّ وَقَدْ تَكَلَّمَ فِيهِ بَعْضُ أَهْلِ الْحَدِيثِ مِنْ قِبَلِ حِفْظِهِ وَلَهُ غَرَائِبُ ‏.</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>অন্যের চেয়ে ভালোভাবে কুরআনের তাৎপর্য আমার জানা থাকা সত্ত্বেও আমি রাসূলুল্লাহ (صلى الله عليه وسلم)-এর যে কোনো সাহাবীর নিকট তার তাৎপর্য জানতে চাইতাম এ উদ্দেশ্যে যাতে তিনি আমাকে (তাঁর বাড়িতে নিয়ে) কিছু খাওয়ান। আমি জাফর ইবনু আবু তালিব (রাঃ)-কে প্রশ্ন করলেই তিনি আমাকে জবাব না দিয়ে তাঁর বাড়িতে নিয়ে যেতেন, তারপর তাঁর স্ত্রীকে বলতেন, হে আসমা! আমাদেরকে খানা খাওয়াও। তাঁর স্ত্রী আমাদের খানা খাওয়ানোর পর তিনি আমার প্রশ্নের উত্তর দিতেন। জাফর (রাঃ) ছিলেন দরিদ্রবৎসল এবং তিনি তাঁদের সাথে উঠাবসা করতেন, তাঁদের সাথে আলাপ-আলোচনা করতেন এবং তাঁরাও তাঁর সাথে কথাবার্তা বলত। তাই রাসূলুল্লাহ (صلى الله عليه وسلم) তাঁকে আবুল মাসাকীন (গরীবদের পিতা) উপনামে আখ্যায়িত করেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>3767</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَبُو أَحْمَدُ، حَاتِمُ بْنُ سِيَاهٍ الْمَرْوَزِيُّ حَدَّثَنَا عَبْدُ الرَّزَّاقِ، أَخْبَرَنَا مَعْمَرٌ، عَنِ ابْنِ عَجْلاَنَ، عَنْ يَزِيدَ بْنِ قُسَيْطٍ، عَنْ أَبِي سَلَمَةَ، عَنْ أَبِي هُرَيْرَةَ، قَالَ كُنَّا نَدْعُو جَعْفَرَ بْنَ أَبِي طَالِبٍ رضى الله عنه أَبَا الْمَسَاكِينِ فَكُنَّا إِذَا أَتَيْنَاهُ قَرَّبْنَا إِلَيْهِ مَا حَضَرَ فَأَتَيْنَاهُ يَوْمًا فَلَمْ يَجِدْ عِنْدَهُ شَيْئًا فَأَخْرَجَ جَرَّةً مِنْ عَسَلٍ فَكَسَرَهَا فَجَعَلْنَا نَلْعَقُ مِنْهَا ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ مِنْ حَدِيثِ أَبِي سَلَمَةَ عَنْ أَبِي هُرَيْرَةَ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>আমরা জা’ফর ইবন আবু তালিব (রাঃ)-কে আবুল মাসাকিন বলে সম্বোধন করতাম। আমরা যখন তার নিকট আগমন করতাম, উপস্থিত যা থাকতো তাই আমাদের সামনে নিয়ে আসত। একদিন আমরা তার নিকট আগমন করলে তিনি কিছুই পেলেন না, ফলে তিনি একটি মধুর মটকা নিয়ে এলেন এবং তা ভেঙে ফেললেন, তারপর আমরা চেটে চেটে খেতে থাকলাম।</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>3768</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مَحْمُودُ بْنُ غَيْلاَنَ، حَدَّثَنَا أَبُو دَاوُدَ الْحَفَرِيُّ، عَنْ سُفْيَانَ، عَنْ يَزِيدَ بْنِ أَبِي زِيَادٍ، عَنِ ابْنِ أَبِي نُعْمٍ، عَنْ أَبِي سَعِيدٍ الْخُدْرِيِّ، رضى الله عنه قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ الْحَسَنُ وَالْحُسَيْنُ سَيِّدَا شَبَابِ أَهْلِ الْجَنَّةِ ‏"‏ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেন: আল-হাসান ও আল-হুসাইন (রাঃ) প্রত্যেকেই জান্নাতী যুবকদের সরদার।</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>3769</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا سُفْيَانُ بْنُ وَكِيعٍ، وَعَبْدُ بْنُ حُمَيْدٍ، قَالاَ حَدَّثَنَا خَالِدُ بْنُ مَخْلَدٍ، حَدَّثَنَا مُوسَى بْنُ يَعْقُوبَ الزَّمْعِيُّ، عَنْ عَبْدِ اللَّهِ بْنِ أَبِي بَكْرِ بْنِ زَيْدِ بْنِ الْمُهَاجِرِ، أَخْبَرَنِي مُسْلِمُ بْنُ أَبِي سَهْلٍ النَّبَّالُ، أَخْبَرَنِي الْحَسَنُ بْنُ أُسَامَةَ بْنِ زَيْدٍ، أَخْبَرَنِي أَبِي أُسَامَةُ بْنُ زَيْدٍ، قَالَ طَرَقْتُ النَّبِيَّ صلى الله عليه وسلم ذَاتَ لَيْلَةٍ فِي بَعْضِ الْحَاجَةِ فَخَرَجَ النَّبِيُّ صلى الله عليه وسلم وَهُوَ مُشْتَمِلٌ عَلَى شَيْءٍ لاَ أَدْرِي مَا هُوَ فَلَمَّا فَرَغْتُ مِنْ حَاجَتِي قُلْتُ مَا هَذَا الَّذِي أَنْتَ مُشْتَمِلٌ عَلَيْهِ قَالَ فَكَشَفَهُ فَإِذَا حَسَنٌ وَحُسَيْنٌ عَلَيْهِمَا السَّلاَمُ عَلَى وَرِكَيْهِ فَقَالَ ‏ "‏ هَذَانِ ابْنَاىَ وَابْنَا ابْنَتِي اللَّهُمَّ إِنِّي أُحِبُّهُمَا فَأَحِبَّهُمَا وَأَحِبَّ مَنْ يُحِبُّهُمَا ‏"‏ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>এক রাতে আমার কোন দরকারে নবী (صلى الله عليه وسلم)-এর কাছে গেলাম। অতএব নবী (صلى الله عليه وسلم) এমন অবস্থায় বাইরে এলেন যে, একটা কিছু তাঁর পিঠে জড়ানো ছিল যা আমি অবগত ছিলাম না। আমি আমার দরকার সেরে অবসর হয়ে প্রশ্ন করলাম, আপনার দেহের সঙ্গে জড়ানো এটা কি? তিনি পরিধেয় বস্ত্র উন্মুক্ত করলে দেখা গেলো তাঁর দুই কোলে হাসান ও হুসাইন (রাঃ)। তিনি বললেন, এরা দু’জন আমার পুত্র এবং আমার কন্যার পুত্র। হে আল্লাহ! আমি এদের দু’জনকে মুহাব্বত করি। সুতরাং তুমি তাদেরকে মুহাব্বত কর এবং যে ব্যক্তি এদেরকে মুহাব্বত করবে, তুমি তাদেরকেও মুহাব্বত কর।</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>3770</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عُقْبَةُ بْنُ مُكْرَمٍ الْعَمِّيُّ، حَدَّثَنَا وَهْبُ بْنُ جَرِيرِ بْنِ حَازِمٍ، حَدَّثَنَا أَبِي، عَنْ مُحَمَّدِ بْنِ أَبِي يَعْقُوبَ، عَنْ عَبْدِ الرَّحْمَنِ بْنِ أَبِي نُعْمٍ، أَنَّ رَجُلاً، مِنْ أَهْلِ الْعِرَاقِ سَأَلَ ابْنَ عُمَرَ عَنْ دَمِ الْبَعُوضِ يُصِيبُ الثَّوْبَ فَقَالَ ابْنُ عُمَرَ انْظُرُوا إِلَى هَذَا يَسْأَلُ عَنْ دَمِ الْبَعُوضِ وَقَدْ قَتَلُوا ابْنَ رَسُولِ اللَّهِ صلى الله عليه وسلم وَسَمِعْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم يَقُولُ ‏ "‏ إِنَّ الْحَسَنَ وَالْحُسَيْنَ هُمَا رَيْحَانَتَاىَ مِنَ الدُّنْيَا ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ صَحِيحٌ ‏.‏ وَقَدْ رَوَاهُ شُعْبَةُ وَمَهْدِيُّ بْنُ مَيْمُونٍ عَنْ مُحَمَّدِ بْنِ أَبِي يَعْقُوبَ ‏.‏ وَقَدْ رُوِيَ عَنْ أَبِي هُرَيْرَةَ عَنِ النَّبِيِّ صلى الله عليه وسلم نَحْوُ هَذَا ‏.‏</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>এক ইরাকবাসী মাছির রক্ত কাপড়ে লাগলে তার বিধান প্রসঙ্গে ইবনু উমর (রাঃ)-এর কাছে জানতে চায়। ইবনু উমর (রাঃ) বললেন, তোমরা তার প্রতি লক্ষ্য কর, সে মশার রক্ত প্রসঙ্গে প্রশ্ন করছে। অথচ তারাই রাসূলুল্লাহ (صلى الله عليه وسلم)-এর পুত্রকে (নাতি হুসাইন) হত্যা করেছে। রাসূলুল্লাহ (صلى الله عليه وسلم)-কে আমি বলতে শুনেছি: আল-হাসান ও আল-হুসাইন দু’জন এই পৃথিবীতে আমার দু’টি সুগন্ধময় ফুল।</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَبُو سَعِيدٍ الأَشَجُّ، حَدَّثَنَا أَبُو خَالِدٍ الأَحْمَرُ، حَدَّثَنَا رَزِينٌ، قَالَ حَدَّثَتْنِي سَلْمَى، قَالَتْ دَخَلْتُ عَلَى أُمِّ سَلَمَةَ وَهِيَ تَبْكِي فَقُلْتُ مَا يُبْكِيكِ قَالَتْ رَأَيْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم - تَعْنِي فِي الْمَنَامِ - وَعَلَى رَأْسِهِ وَلِحْيَتِهِ التُّرَابُ فَقُلْتُ مَا لَكَ يَا رَسُولَ اللَّهِ ‏.‏ قَالَ ‏ "‏ شَهِدْتُ قَتْلَ الْحُسَيْنِ آنِفًا ‏"‏ ‏.‏ قَالَ هَذَا حَدِيثٌ غَرِيبٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>আমি উম্মু সালামা (রাঃ)-এর নিকট গিয়েছিলাম, তখন তিনি কাঁদছিলেন। আমি বললাম, কিসে আপনাকে কাঁদাচ্ছে? তিনি বললেন, আমি স্বপ্নে রাসূলুল্লাহ (صلى الله عليه وسلم)-কে দেখেছি যে, তাঁর মাথায় ও দাড়িতে ধূলা জড়িয়ে আছে। আমি বললাম, হে আল্লাহর রাসূল! আপনার কি হয়েছে? তিনি বললেনঃ আমি এইমাত্র হুসাইনের নিহত হওয়ার জায়গায় হাযির হয়েছি।</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا أَبُو سَعِيدٍ الأَشَجُّ، حَدَّثَنَا عُقْبَةُ بْنُ خَالِدٍ، حَدَّثَنِي يُوسُفُ بْنُ إِبْرَاهِيمَ، أَنَّهُ سَمِعَ أَنَسَ بْنَ مَالِكٍ، يَقُولُ سُئِلَ رَسُولُ اللَّهِ صلى الله عليه وسلم أَىُّ أَهْلِ بَيْتِكَ أَحَبُّ إِلَيْكَ قَالَ ‏"‏ الْحَسَنُ وَالْحُسَيْنُ ‏"‏ ‏.‏ وَكَانَ يَقُولُ لِفَاطِمَةَ ‏"‏ ادْعِي لِي ابْنَىَّ ‏"‏ ‏.‏ فَيَشُمُّهُمَا وَيَضُمُّهُمَا إِلَيْهِ ‏.‏ قَالَ هَذَا حَدِيثٌ غَرِيبٌ مِنْ هَذَا الْوَجْهِ مِنْ حَدِيثِ أَنَسٍ</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم)-কে প্রশ্ন করা হল, আপনার আহলে বাইতের সদস্যগণের মধ্যে কে আপনার নিকট সবচাইতে প্রিয়? তিনি বললেনঃ আল-হাসান ও আল-হুসাইন। তিনি ফাতিমা (রাঃ)-কে বলতেনঃ আমার দুই সন্তানকে আমার কাছে ডাক। তিনি তাদের ঘ্রাণ নিতেন এবং নিজের বুকের সাথে লাগাতেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>3774</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا الْحُسَيْنُ بْنُ حُرَيْثٍ، حَدَّثَنَا عَلِيُّ بْنُ حُسَيْنِ بْنِ وَاقِدٍ، حَدَّثَنِي أَبِي، حَدَّثَنِي عَبْدُ اللَّهِ بْنُ بُرَيْدَةَ، قَالَ سَمِعْتُ أَبِي، ‏:‏ بُرَيْدَةَ يَقُولُ كَانَ رَسُولُ اللَّهِ صلى الله عليه وسلم يَخْطُبُنَا إِذْ جَاءَ الْحَسَنُ وَالْحُسَيْنُ عَلَيْهِمَا السَّلاَمُ عَلَيْهِمَا قَمِيصَانِ أَحْمَرَانِ يَمْشِيَانِ وَيَعْثُرَانِ فَنَزَلَ رَسُولُ اللَّهِ صلى الله عليه وسلم مِنَ الْمِنْبَرِ فَحَمَلَهُمَا وَوَضَعَهُمَا بَيْنَ يَدَيْهِ ثُمَّ قَالَ ‏"‏ صَدَقَ اللَّهُ ‏:‏ ‏(‏ إنَّمَا أَمْوَالُكُمْ وَأَوْلاَدُكُمْ فِتْنَةٌ ‏)‏ فَنَظَرْتُ إِلَى هَذَيْنِ الصَّبِيَّيْنِ يَمْشِيَانِ وَيَعْثُرَانِ فَلَمْ أَصْبِرْ حَتَّى قَطَعْتُ حَدِيثِي وَرَفَعْتُهُمَا ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ غَرِيبٌ إِنَّمَا نَعْرِفُهُ مِنْ حَدِيثِ الْحُسَيْنِ بْنِ وَاقِدٍ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>আমি আমার পিতা বুরাইদা (রাঃ)-কে বলতে শুনেছি, রাসূলুল্লাহ (صلى الله عليه وسلم) আমাদের উদ্দেশে ভাষণ দিচ্ছিলেন। হঠাৎ হাসান ও হুসাইন (আঃ) লাল বর্ণের জামা পরিহিত অবস্থায় (শিশু হওয়ার কারণে) আছাড় খেতে খেতে হেঁটে আসেন। রাসূলুল্লাহ (صلى الله عليه وسلم) মিম্বার হতে নেমে তাদের দু’জনকে তুলে এনে নিজের সম্মুখে বসান, তারপর বলেনঃ আল্লাহ তা‘আলা সত্যই বলেছেন, “তোমাদের সম্পদ ও তোমাদের সন্তান-সন্ততি তো পরীক্ষা বিশেষ”-(সূরা তাগাবুন ১৫)। আমি তাকিয়ে দেখলাম এই শিশু দু’টি আছাড় খেতে খেতে হেঁটে আসছে। আমি আর সহ্য করতে পারলাম না, এমনকি আমার বক্তৃতা বন্ধ করে তাদেরকে তুলে নিতে বাধ্য হলাম।</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>3775</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا الْحَسَنُ بْنُ عَرَفَةَ، حَدَّثَنَا إِسْمَاعِيلُ بْنُ عَيَّاشٍ، عَنْ عَبْدِ اللَّهِ بْنِ عُثْمَانَ بْنِ خُثَيْمٍ، عَنْ سَعِيدِ بْنِ رَاشِدٍ، عَنْ يَعْلَى بْنِ مُرَّةَ، قَالَ قَالَ رَسُولُ اللَّهِ صلى الله عليه وسلم ‏ "‏ حُسَيْنٌ مِنِّي وَأَنَا مِنْ حُسَيْنٍ أَحَبَّ اللَّهُ مَنْ أَحَبَّ حُسَيْنًا حُسَيْنٌ سِبْطٌ مِنَ الأَسْبَاطِ ‏"‏ ‏.‏ قَالَ أَبُو عِيسَى هَذَا حَدِيثٌ حَسَنٌ وَإِنَّمَا نَعْرِفُهُ مِنْ حَدِيثِ عَبْدِ اللَّهِ بْنِ عُثْمَانَ بْنِ خُثَيْمٍ وَقَدْ رَوَاهُ غَيْرُ وَاحِدٍ عَنْ عَبْدِ اللَّهِ بْنِ عُثْمَانَ بْنِ خُثَيْمٍ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم) বলেছেনঃ হুসাইন আমার হতে এবং আমি হুসাইন হতে। যে লোক হুসাইনকে মহব্বত করে, আল্লাহ তাকে মহব্বত করেন। নাতিগণের মাঝে একজন হল হুসাইন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>3776</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ يَحْيَى، حَدَّثَنَا عَبْدُ الرَّزَّاقِ، عَنْ مَعْمَرٍ، عَنِ الزُّهْرِيِّ، عَنْ أَنَسِ بْنِ مَالِكٍ، قَالَ لَمْ يَكُنْ مِنْهُمْ أَحَدٌ أَشْبَهَ بِرَسُولِ اللَّهِ مِنَ الْحَسَنِ بْنِ عَلِيٍّ ‏.‏ قَالَ هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>লোকদের মাঝে দৈহিক কাঠামোয় রাসূলুল্লাহ (صلى الله عليه وسلم)-এর সঙ্গে আল-হাসান ইবন আলীর তুলনায় বেশি সাদৃশ্যপূর্ণ আর কেউ ছিল না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>3777</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا مُحَمَّدُ بْنُ بَشَّارٍ، حَدَّثَنَا يَحْيَى بْنُ سَعِيدٍ، حَدَّثَنَا إِسْمَاعِيلُ بْنُ أَبِي خَالِدٍ، عَنْ أَبِي جُحَيْفَةَ، قَالَ رَأَيْتُ رَسُولَ اللَّهِ صلى الله عليه وسلم وَكَانَ الْحَسَنُ بْنُ عَلِيٍّ يُشْبِهُهُ ‏.‏ هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏ قَالَ وَفِي الْبَابِ عَنْ أَبِي بَكْرٍ الصِّدِّيقِ وَابْنِ عَبَّاسٍ وَابْنِ الزُّبَيْرِ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم)-কে আমি দেখেছি। আল-হাসান ইবন আলী ছিলেন (দৈহিক কাঠামোয়) তাঁর সঙ্গে সাদৃশ্যপূর্ণ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>3779</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا عَبْدُ اللَّهِ بْنُ عَبْدِ الرَّحْمَنِ، أَخْبَرَنَا عُبَيْدُ اللَّهِ بْنُ مُوسَى، عَنْ إِسْرَائِيلَ، عَنْ أَبِي إِسْحَاقَ، عَنْ هَانِئِ بْنِ هَانِئٍ، عَنْ عَلِيٍّ، قَالَ الْحَسَنُ أَشْبَهُ بِرَسُولِ اللَّهِ صلى الله عليه وسلم مَا بَيْنَ الصَّدْرِ إِلَى الرَّأْسِ وَالْحُسَيْنُ أَشْبَهُ بِالنَّبِيِّ صلى الله عليه وسلم مَا كَانَ أَسْفَلَ مِنْ ذَلِكَ ‏.‏ هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ غَرِيبٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>রাসূলুল্লাহ (صلى الله عليه وسلم)-এর বুক হতে মাথা পর্যন্ত অংশের সাথে হাসান (রাঃ)-এর শরীরের সাদৃশ্য ছিল এবং রাসূলুল্লাহ (صلى الله عليه وسلم)-এর বুক হতে পা পর্যন্ত নিচের অংশের সাথে হুসাইন (রাঃ)-এর শরীরের সাদৃশ্য ছিল।</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>حَدَّثَنَا وَاصِلُ بْنُ عَبْدِ الأَعْلَى، حَدَّثَنَا أَبُو مُعَاوِيَةَ، عَنِ الأَعْمَشِ، عَنْ عُمَارَةَ بْنِ عُمَيْرٍ، قَالَ لَمَّا جِيءَ بِرَأْسِ عُبَيْدِ اللَّهِ بْنِ زِيَادٍ وَأَصْحَابِهِ نُضِّدَتْ فِي الْمَسْجِدِ فِي الرَّحَبَةِ فَانْتَهَيْتُ إِلَيْهِمْ وَهُمْ يَقُولُونَ قَدْ جَاءَتْ قَدْ جَاءَتْ ‏.‏ فَإِذَا حَيَّةٌ قَدْ جَاءَتْ تَخَلَّلُ الرُّءُوسَ حَتَّى دَخَلَتْ فِي مَنْخَرَىْ عُبَيْدِ اللَّهِ بْنِ زِيَادٍ فَمَكَثَتْ هُنَيْهَةً ثُمَّ خَرَجَتْ فَذَهَبَتْ حَتَّى تَغَيَّبَتْ ثُمَّ قَالُوا قَدْ جَاءَتْ قَدْ جَاءَتْ ‏.‏ فَفَعَلَتْ ذَلِكَ مَرَّتَيْنِ أَوْ ثَلاَثًا ‏.‏ هَذَا حَدِيثٌ حَسَنٌ صَحِيحٌ ‏.‏</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>উবাইদুল্লাহ ইবনু জিয়াদ ও তার সাথীদের ছিন্ন মস্তক এনে কুফার 'রাহবা' নামক জায়গায় মসজিদে স্তূপীকৃত করা হলে আমি সেখানে গেলাম। সে সময় লোকেরা এসে গেছে, এসে গেছে বলে চেঁচামিচি করতে লাগল। দেখা গেল একটি সাপ এসে ঐসব মাথাসমূহের অভ্যন্তরে ঢুকে পড়ছিল। এমনকি সাপটি উবাইদুল্লাহ ইবনু জিয়াদের নাকের ছিদ্রে প্রবেশ করে কিছুক্ষণ সেখানে অবস্থান করল, তারপর বের হয়ে অদৃশ্য হয়ে গেল। লোকেরা আবারও চিৎকার করে বলতে লাগল, এসে গেছে, এসে গেছে। এরূপে সাপটি দুবার অথবা তিনবার এসে তার নাকের ছিদ্রে ঢুকে কিছুক্ষণ অবস্থান করার পর বের হয়ে যায়।</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
